--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R65e8b62d37c54fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R342d775b3c2148b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R05a756a7417d4ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R027d48a9707e463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Rdc9876a903ef4fda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Rc86dc48e83144aba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R13fdf6124aea4caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R29aca89dcef54fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R18a22b517019465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R1e2f4085e075453d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="Ra773dfd67c834a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R5714d99ffe8c4182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="Rd724abbf05cd4abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R7a42803be5e24a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Rc4d5776214704208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rd70a2c68d87a4a4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R6682b37d56a24093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R63a0114a9559425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Ra8a20845ebda481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Rae6ff21234a440a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R111c622533fb4402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="Rf01fb911478b46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R9336df5a65df425f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R482dfe65825b48e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="Rf955a9bfb2124656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="Rf64454b413fd4f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R30677a2b9ae04cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R19cef98dad454bff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,8 +60,18 @@
       <x:color rgb="FF216E39"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF8A6D1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF2E7D32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="33">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -213,6 +223,16 @@
         <x:fgColor rgb="FFE8F3EC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -260,7 +280,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="75">
+  <x:cellXfs count="79">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -470,6 +490,18 @@
     <x:xf numFmtId="0" fontId="5" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2278,18 +2310,18 @@
         <x:color rgb="FF7A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF216E39"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF216E39"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
@@ -2300,7 +2332,7 @@
         <x:color rgb="FF9C2F23"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2310,18 +2342,18 @@
         <x:color rgb="FF7A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF216E39"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF216E39"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
@@ -2332,7 +2364,7 @@
         <x:color rgb="FF9C2F23"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2342,18 +2374,18 @@
         <x:color rgb="FF7A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF216E39"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF216E39"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
@@ -2364,7 +2396,7 @@
         <x:color rgb="FF9C2F23"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2374,18 +2406,18 @@
         <x:color rgb="FF7A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF216E39"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF216E39"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
@@ -2396,7 +2428,7 @@
         <x:color rgb="FF9C2F23"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2406,18 +2438,18 @@
         <x:color rgb="FF7A5200"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF216E39"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF216E39"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE8F3EC"/>
         </x:patternFill>
       </x:fill>
@@ -2428,7 +2460,7 @@
         <x:color rgb="FF9C2F23"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -2719,10 +2751,10 @@
         <x:v>Keyboard</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
-        <x:v>This matrix applies on desktop and on mobile when a hardware keyboard is present.</x:v>
+        <x:v>This matrix applies on desktop and on mobile when a hardware keyboard is present. Ctrl edits selection; Option temporarily reveals selection neighbors and connecting links.</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="21" t="str">
         <x:v>Open</x:v>
@@ -2857,7 +2889,7 @@
         <x:v>Resolved decisions from UI contract review.</x:v>
       </x:c>
       <x:c r="C18" s="19" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D18" s="20" t="str">
         <x:v>Approved</x:v>
@@ -3734,12 +3766,12 @@
         <x:v>Conditional Center + Fit</x:v>
       </x:c>
       <x:c r="C12" s="19" t="str">
-        <x:v>While Ctrl is held, undim direct neighbors of the current selection and update that reveal as selection changes. On release, restore normal dimming. Center + Fit only after an initial selection that began empty; otherwise no camera change.</x:v>
+        <x:v>Center + Fit only after an initial selection that began empty; otherwise no camera change.</x:v>
       </x:c>
       <x:c r="D12" s="20" t="str">
         <x:v>Approved</x:v>
       </x:c>
-      <x:c r="E12" s="19" t="str"/>
+      <x:c r="E12" s="19"/>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -3755,6 +3787,21 @@
         <x:v>Approved</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str"/>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
+      <x:c r="A14" s="43" t="str">
+        <x:v>Option neighbor reveal</x:v>
+      </x:c>
+      <x:c r="B14" s="43" t="str">
+        <x:v>Transient selection presentation</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="str">
+        <x:v>While Option is held, undim direct neighbors of the current selection and the links connecting them to the selection. Update the reveal as selection changes. On release, restore normal dimming without changing selection, focus, or camera.</x:v>
+      </x:c>
+      <x:c r="D14" s="78" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E14" s="43"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D13">
@@ -3762,9 +3809,12 @@
     <x:cfRule type="containsText" dxfId="58" priority="2" operator="containsText" text="Change"/>
     <x:cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Open"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="D6:D13">
       <x:formula1>"Open,Approved,Change"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D14">
+      <x:formula1>"Open,Approved,Needs changes"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4262,7 +4312,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E14" s="19" t="str">
-        <x:v>Update selection and centroid without moving focus; while Ctrl is held, undim direct neighbors of the current selection</x:v>
+        <x:v>Update selection and centroid without moving focus</x:v>
       </x:c>
       <x:c r="F14" s="19" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -4286,7 +4336,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>Update selection and centroid without moving focus; while Ctrl is held, undim direct neighbors of the current selection</x:v>
+        <x:v>Update selection and centroid without moving focus</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -4310,7 +4360,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E16" s="19" t="str">
-        <x:v>Keep resulting selection; set focus to its centroid; restore normal selection dimming</x:v>
+        <x:v>Keep resulting selection; set focus to its centroid</x:v>
       </x:c>
       <x:c r="F16" s="19" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -4334,7 +4384,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>Keep additions and removals; keep the existing focus point; restore normal selection dimming</x:v>
+        <x:v>Keep additions and removals; keep the existing focus point</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -5034,13 +5084,13 @@
         <x:v>Hold Ctrl</x:v>
       </x:c>
       <x:c r="B13" s="18" t="str">
-        <x:v>Undim direct neighbors of the current selection</x:v>
+        <x:v>Enable additive or removal selection</x:v>
       </x:c>
       <x:c r="C13" s="18" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>While held, reveal direct neighbors and enable additive or removal selection; update the revealed neighborhood as selection changes</x:v>
+        <x:v>Do not change presentation or camera while held; additions and removals recalculate the centroid without moving focus</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -5052,16 +5102,16 @@
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
       <x:c r="A14" s="19" t="str">
-        <x:v>Release Ctrl after editing an existing selection</x:v>
+        <x:v>Hold Option</x:v>
       </x:c>
       <x:c r="B14" s="19" t="str">
-        <x:v>No camera change</x:v>
+        <x:v>Undim direct neighbors of the current selection and the links connecting them to the selection</x:v>
       </x:c>
       <x:c r="C14" s="19" t="str">
-        <x:v>No camera change</x:v>
+        <x:v>Same</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>Keep additions and removals; recalculate the centroid without moving focus; restore normal selection dimming</x:v>
+        <x:v>Do not mutate selection, focus, or camera; update the reveal as selection changes; release restores normal dimming</x:v>
       </x:c>
       <x:c r="E14" s="19" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -5073,16 +5123,16 @@
     </x:row>
     <x:row r="15" ht="43" customHeight="1">
       <x:c r="A15" s="18" t="str">
-        <x:v>Release Ctrl after initial selection</x:v>
+        <x:v>Release Ctrl after editing an existing selection</x:v>
       </x:c>
       <x:c r="B15" s="18" t="str">
-        <x:v>Center + Fit</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
-        <x:v>Center + Fit</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>Keep resulting selection; set focus to its centroid; restore normal selection dimming</x:v>
+        <x:v>Keep additions and removals; recalculate the centroid without moving focus</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -5094,37 +5144,37 @@
     </x:row>
     <x:row r="16" ht="43" customHeight="1">
       <x:c r="A16" s="19" t="str">
-        <x:v>Tab on graph or background</x:v>
+        <x:v>Release Ctrl after initial selection</x:v>
       </x:c>
       <x:c r="B16" s="19" t="str">
-        <x:v>Toggle Quick Settings</x:v>
+        <x:v>Center + Fit</x:v>
       </x:c>
       <x:c r="C16" s="19" t="str">
-        <x:v>Same</x:v>
+        <x:v>Center + Fit</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
-        <x:v>Disabled while typing in a control</x:v>
+        <x:v>Keep resulting selection; set focus to its centroid</x:v>
       </x:c>
       <x:c r="E16" s="19" t="str">
-        <x:v>Current</x:v>
+        <x:v>Confirmed requirement</x:v>
       </x:c>
       <x:c r="F16" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G16" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="G16" s="19"/>
     </x:row>
     <x:row r="17" ht="43" customHeight="1">
       <x:c r="A17" s="18" t="str">
-        <x:v>Shift + Tab</x:v>
+        <x:v>Tab on graph or background</x:v>
       </x:c>
       <x:c r="B17" s="18" t="str">
-        <x:v>Normal reverse focus navigation</x:v>
+        <x:v>Toggle Quick Settings</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>Do not toggle panel</x:v>
+        <x:v>Disabled while typing in a control</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
         <x:v>Current</x:v>
@@ -5132,20 +5182,20 @@
       <x:c r="F17" s="21" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="G17" s="18" t="str"/>
+      <x:c r="G17" s="18"/>
     </x:row>
     <x:row r="18" ht="43" customHeight="1">
       <x:c r="A18" s="19" t="str">
-        <x:v>0 or F</x:v>
+        <x:v>Shift + Tab</x:v>
       </x:c>
       <x:c r="B18" s="19" t="str">
-        <x:v>No graph action</x:v>
+        <x:v>Normal reverse focus navigation</x:v>
       </x:c>
       <x:c r="C18" s="19" t="str">
-        <x:v>No graph action</x:v>
+        <x:v>Same</x:v>
       </x:c>
       <x:c r="D18" s="19" t="str">
-        <x:v>None</x:v>
+        <x:v>Do not toggle panel</x:v>
       </x:c>
       <x:c r="E18" s="19" t="str">
         <x:v>Current</x:v>
@@ -5153,7 +5203,28 @@
       <x:c r="F18" s="20" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="G18" s="19" t="str"/>
+      <x:c r="G18" s="19"/>
+    </x:row>
+    <x:row r="19" ht="43" customHeight="1">
+      <x:c r="A19" s="43" t="str">
+        <x:v>0 or F</x:v>
+      </x:c>
+      <x:c r="B19" s="43" t="str">
+        <x:v>No graph action</x:v>
+      </x:c>
+      <x:c r="C19" s="43" t="str">
+        <x:v>No graph action</x:v>
+      </x:c>
+      <x:c r="D19" s="43" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E19" s="43" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="F19" s="76" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="G19" s="43"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F6:F18">
@@ -5165,9 +5236,12 @@
     <x:cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Confirmed"/>
     <x:cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="Verify"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F6:F18">
       <x:formula1>"Open,Approved,Change"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F19">
+      <x:formula1>"Open,Approved,Needs changes"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Rc4d5776214704208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rd70a2c68d87a4a4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R6682b37d56a24093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R63a0114a9559425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Ra8a20845ebda481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Rae6ff21234a440a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R111c622533fb4402"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="Rf01fb911478b46b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R9336df5a65df425f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R482dfe65825b48e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="Rf955a9bfb2124656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="Rf64454b413fd4f15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R30677a2b9ae04cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R19cef98dad454bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Ra3036747682d4622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R2817250ff5bb47f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R1d2fc27db3c0483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R39d6984029164fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Rf9c2bea826fc4e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R99eaa93ef4cd4097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R74bef573dbd041b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R5473d00fb3ce4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R3bb2c2cd78c94391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R21b758f890064144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="Ra98b58b2463d4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R4c31caa2f86c431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="Rddec7262cf5e482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="Rb129716c536b49aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -233,6 +233,11 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -280,7 +285,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="79">
+  <x:cellXfs count="81">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -500,6 +505,12 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2739,7 +2750,7 @@
         <x:v>A browser usually reports physical mouse-wheel and two-finger trackpad scroll through the same wheel event path.</x:v>
       </x:c>
       <x:c r="C8" s="19" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>Open</x:v>
@@ -2889,7 +2900,7 @@
         <x:v>Resolved decisions from UI contract review.</x:v>
       </x:c>
       <x:c r="C18" s="19" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="20" t="str">
         <x:v>Approved</x:v>
@@ -3790,18 +3801,48 @@
     </x:row>
     <x:row r="14" ht="60" customHeight="1">
       <x:c r="A14" s="43" t="str">
-        <x:v>Option neighbor reveal</x:v>
+        <x:v>Option neighbor highlight</x:v>
       </x:c>
       <x:c r="B14" s="43" t="str">
-        <x:v>Transient selection presentation</x:v>
+        <x:v>Transient hover-equivalent presentation</x:v>
       </x:c>
       <x:c r="C14" s="43" t="str">
-        <x:v>While Option is held, undim direct neighbors of the current selection and the links connecting them to the selection. Update the reveal as selection changes. On release, restore normal dimming without changing selection, focus, or camera.</x:v>
+        <x:v>While Option is held, highlight direct neighbors of the current selection and the links connecting them to the selection using the same treatment as hovering the selected node. Update the highlight as selection changes. On release, restore normal presentation without changing selection, focus, or camera.</x:v>
       </x:c>
       <x:c r="D14" s="78" t="str">
         <x:v>Approved</x:v>
       </x:c>
       <x:c r="E14" s="43"/>
+    </x:row>
+    <x:row r="15" ht="60" customHeight="1">
+      <x:c r="A15" s="43" t="str">
+        <x:v>Tag node selection</x:v>
+      </x:c>
+      <x:c r="B15" s="43" t="str">
+        <x:v>Same as ordinary node selection</x:v>
+      </x:c>
+      <x:c r="C15" s="43" t="str">
+        <x:v>Clicking a tag selects only that tag. Region members remain unselected and do not receive selected-label presentation.</x:v>
+      </x:c>
+      <x:c r="D15" s="80" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E15" s="43"/>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
+      <x:c r="A16" s="43" t="str">
+        <x:v>Cmd-scroll</x:v>
+      </x:c>
+      <x:c r="B16" s="43" t="str">
+        <x:v>Ordinary wheel navigation</x:v>
+      </x:c>
+      <x:c r="C16" s="43" t="str">
+        <x:v>Cmd does not enable zoom. Cmd-scroll follows the same 2D and 3D navigation behavior as unmodified wheel input.</x:v>
+      </x:c>
+      <x:c r="D16" s="80" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E16" s="43"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D13">
@@ -3809,11 +3850,17 @@
     <x:cfRule type="containsText" dxfId="58" priority="2" operator="containsText" text="Change"/>
     <x:cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Open"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="D6:D13">
       <x:formula1>"Open,Approved,Change"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="D14">
+      <x:formula1>"Open,Approved,Needs changes"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D15">
+      <x:formula1>"Open,Approved,Needs changes"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D16">
       <x:formula1>"Open,Approved,Needs changes"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -4231,16 +4278,16 @@
         <x:v>Primary click</x:v>
       </x:c>
       <x:c r="B11" s="18" t="str">
-        <x:v>Node, no existing selection</x:v>
+        <x:v>Node, including tag, with no existing selection</x:v>
       </x:c>
       <x:c r="C11" s="18" t="str">
-        <x:v>On release, select node; then Center + Fit selection</x:v>
+        <x:v>On release, select only the clicked node; then Center + Fit selection</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>Begin selection; set focus point to the calculated selection centroid</x:v>
+        <x:v>Begin selection with only the clicked node; set focus point to the calculated selection centroid</x:v>
       </x:c>
       <x:c r="F11" s="18" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -4255,16 +4302,16 @@
         <x:v>Primary click</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>Node, existing selection</x:v>
+        <x:v>Node, including tag, with an existing selection</x:v>
       </x:c>
       <x:c r="C12" s="19" t="str">
-        <x:v>On release, add node and shortest-path bridge; no camera change</x:v>
+        <x:v>On release, add the clicked node and shortest-path bridge; no camera change</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E12" s="19" t="str">
-        <x:v>Accumulate selection and recalculate its centroid; keep the existing focus point</x:v>
+        <x:v>Accumulate the clicked node and bridge; recalculate the centroid; keep the existing focus point</x:v>
       </x:c>
       <x:c r="F12" s="19" t="str">
         <x:v>Confirmed requirement</x:v>
@@ -4864,6 +4911,27 @@
       </x:c>
       <x:c r="G13" s="18" t="str"/>
     </x:row>
+    <x:row r="14" ht="43" customHeight="1">
+      <x:c r="A14" s="43" t="str">
+        <x:v>Cmd + two-finger scroll or wheel</x:v>
+      </x:c>
+      <x:c r="B14" s="43" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="C14" s="43" t="str">
+        <x:v>Same as unmodified</x:v>
+      </x:c>
+      <x:c r="D14" s="43" t="str">
+        <x:v>Same as unmodified</x:v>
+      </x:c>
+      <x:c r="E14" s="43" t="str">
+        <x:v>Cmd does not enable zoom</x:v>
+      </x:c>
+      <x:c r="F14" s="80" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="G14" s="43"/>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F6:F13">
     <x:cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="Approved"/>
@@ -4874,9 +4942,12 @@
     <x:cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="Confirmed"/>
     <x:cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Verify"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F6:F13">
       <x:formula1>"Open,Approved,Change"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F14">
+      <x:formula1>"Open,Approved,Needs changes"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5105,13 +5176,13 @@
         <x:v>Hold Option</x:v>
       </x:c>
       <x:c r="B14" s="19" t="str">
-        <x:v>Undim direct neighbors of the current selection and the links connecting them to the selection</x:v>
+        <x:v>Highlight direct neighbors of the current selection and the links connecting them to the selection</x:v>
       </x:c>
       <x:c r="C14" s="19" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>Do not mutate selection, focus, or camera; update the reveal as selection changes; release restores normal dimming</x:v>
+        <x:v>Use the same highlight treatment as hovering the selected node; do not mutate selection, focus, or camera; release restores normal selection presentation</x:v>
       </x:c>
       <x:c r="E14" s="19" t="str">
         <x:v>Confirmed requirement</x:v>

--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Ra3036747682d4622"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R2817250ff5bb47f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R1d2fc27db3c0483c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R39d6984029164fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Rf9c2bea826fc4e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R99eaa93ef4cd4097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R74bef573dbd041b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R5473d00fb3ce4f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R3bb2c2cd78c94391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R21b758f890064144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="Ra98b58b2463d4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R4c31caa2f86c431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="Rddec7262cf5e482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="Rb129716c536b49aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R67eaa48484b342ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R1b9068ba29024758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R80827e993d564b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="Rcff5a4f6383c491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="R80cc330924df4b46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R20dcd0a9aed14a9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="Rb2d5c2b1756049f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R92f0485f2e664292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R7922007b4a4e4adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Re268440acfbc49a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R60e199a014e0472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="Rf3c03185b98f41ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R3726414233ec42f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="Ra3dc5d7ab4c34f32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5343,7 +5343,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>Two-finger behavior is defined separately. One-finger background behavior remains open for review.</x:v>
+        <x:v>Two-finger behavior is defined separately. One-finger background drag pans in 2D and rotates the camera in 3D.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -5455,13 +5455,13 @@
         <x:v>Pan</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>Currently pans</x:v>
+        <x:v>Rotate camera</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>Preserve selection state; pan translates the stored focus point</x:v>
+        <x:v>No selection change; 2D pan translates the stored focus point and 3D rotate uses it</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>Verify intended 3D behavior</x:v>
+        <x:v>Confirmed requirement</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>Approved</x:v>

--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,20 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R67eaa48484b342ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R1b9068ba29024758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R80827e993d564b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="Rcff5a4f6383c491a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="R80cc330924df4b46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R20dcd0a9aed14a9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="Rb2d5c2b1756049f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R92f0485f2e664292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R7922007b4a4e4adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Re268440acfbc49a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R60e199a014e0472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="Rf3c03185b98f41ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R3726414233ec42f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="Ra3dc5d7ab4c34f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Rcfd0f9b4156c4995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rdd49707a76cb4b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="Rdcf6c81473214bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R11c0f3b7a157433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Ra2c6f2646cee46c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R54a5b1f2059040d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R5e7a25f455b2438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R4324de4c009c4e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R3cf89ac732934a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Rf89cde0c37f74a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R49081ccca45e4558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R322368a5ede9427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="Rcaa7840dae554503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R829c9ad958fc431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Policies" sheetId="15" r:id="Rf0ccd3ada4664672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="16" r:id="R0426697231f84912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Focus Rendering" sheetId="17" r:id="R9623b98e3cb14706"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -70,8 +73,43 @@
       <x:color rgb="FF2E7D32"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF24313D"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF24384D"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF66727F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF256E3F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF8A5B00"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="44">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -238,8 +276,58 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24384D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F3EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24384D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F3EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="7">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -281,11 +369,25 @@
         <x:color rgb="FFCFD7DF"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCFD8E3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCFD8E3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCFD8E3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCFD8E3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="108">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -513,6 +615,85 @@
     <x:xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="36" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="36" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="37" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="38" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="38" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="40" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="41" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="41" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="42" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="43" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="43" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2478,6 +2659,197 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="ReviewIndexContract" displayName="ReviewIndexContract" ref="A5:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Worksheet"/>
+    <x:tableColumn id="2" name="Scope"/>
+    <x:tableColumn id="3" name="Rows"/>
+    <x:tableColumn id="4" name="Review decision"/>
+    <x:tableColumn id="5" name="Reviewer notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="NodeContextMenuContract" displayName="NodeContextMenuContract" ref="A5:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Action"/>
+    <x:tableColumn id="2" name="Result"/>
+    <x:tableColumn id="3" name="Availability"/>
+    <x:tableColumn id="4" name="Selection / Focus effect"/>
+    <x:tableColumn id="5" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="OpenDecisionsContract" displayName="OpenDecisionsContract" ref="A5:C8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="Topic"/>
+    <x:tableColumn id="2" name="Current decision"/>
+    <x:tableColumn id="3" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="StatePoliciesContract" displayName="StatePoliciesContract" ref="A5:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="State"/>
+    <x:tableColumn id="2" name="Selection"/>
+    <x:tableColumn id="3" name="Focused node"/>
+    <x:tableColumn id="4" name="Camera target"/>
+    <x:tableColumn id="5" name="Center + Fit target"/>
+    <x:tableColumn id="6" name="Render scope"/>
+    <x:tableColumn id="7" name="Primary 2D"/>
+    <x:tableColumn id="8" name="Primary 3D"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="StateTransitionsContract" displayName="StateTransitionsContract" ref="A5:G15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="From"/>
+    <x:tableColumn id="2" name="Input"/>
+    <x:tableColumn id="3" name="Guard"/>
+    <x:tableColumn id="4" name="To"/>
+    <x:tableColumn id="5" name="Selection effect"/>
+    <x:tableColumn id="6" name="Focus effect"/>
+    <x:tableColumn id="7" name="Camera / action"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="FocusRenderingContract" displayName="FocusRenderingContract" ref="A5:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="Element"/>
+    <x:tableColumn id="2" name="Node presentation"/>
+    <x:tableColumn id="3" name="Label presentation"/>
+    <x:tableColumn id="4" name="Link presentation"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="StateDefinitionsContract" displayName="StateDefinitionsContract" ref="A5:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Term"/>
+    <x:tableColumn id="2" name="Definition"/>
+    <x:tableColumn id="3" name="Contract significance"/>
+    <x:tableColumn id="4" name="Camera / render consequence"/>
+    <x:tableColumn id="5" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="DesktopPointerContract" displayName="DesktopPointerContract" ref="A5:G26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="Input"/>
+    <x:tableColumn id="2" name="Target / state"/>
+    <x:tableColumn id="3" name="2D behavior"/>
+    <x:tableColumn id="4" name="3D behavior"/>
+    <x:tableColumn id="5" name="Selection / Focus effect"/>
+    <x:tableColumn id="6" name="Camera effect"/>
+    <x:tableColumn id="7" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="DesktopTrackpadContract" displayName="DesktopTrackpadContract" ref="A5:F13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Input"/>
+    <x:tableColumn id="2" name="State / target"/>
+    <x:tableColumn id="3" name="2D behavior"/>
+    <x:tableColumn id="4" name="3D behavior"/>
+    <x:tableColumn id="5" name="State / camera effect"/>
+    <x:tableColumn id="6" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="KeyboardContract" displayName="KeyboardContract" ref="A5:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Input"/>
+    <x:tableColumn id="2" name="2D behavior"/>
+    <x:tableColumn id="3" name="3D behavior"/>
+    <x:tableColumn id="4" name="State / camera effect"/>
+    <x:tableColumn id="5" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="MobileTouchContract" displayName="MobileTouchContract" ref="A5:G23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="Input"/>
+    <x:tableColumn id="2" name="Target / state"/>
+    <x:tableColumn id="3" name="2D behavior"/>
+    <x:tableColumn id="4" name="3D behavior"/>
+    <x:tableColumn id="5" name="Selection / Focus effect"/>
+    <x:tableColumn id="6" name="Camera / action"/>
+    <x:tableColumn id="7" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MobileTwoFingerContract" displayName="MobileTwoFingerContract" ref="A5:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Gesture"/>
+    <x:tableColumn id="2" name="State"/>
+    <x:tableColumn id="3" name="2D behavior"/>
+    <x:tableColumn id="4" name="3D behavior"/>
+    <x:tableColumn id="5" name="Selection / Focus effect"/>
+    <x:tableColumn id="6" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="StylusContract" displayName="StylusContract" ref="A5:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Input"/>
+    <x:tableColumn id="2" name="Target / state"/>
+    <x:tableColumn id="3" name="2D behavior"/>
+    <x:tableColumn id="4" name="3D behavior"/>
+    <x:tableColumn id="5" name="State effect"/>
+    <x:tableColumn id="6" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="CenteringContract" displayName="CenteringContract" ref="A5:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Action"/>
+    <x:tableColumn id="2" name="Target"/>
+    <x:tableColumn id="3" name="Operation"/>
+    <x:tableColumn id="4" name="Must remain unchanged"/>
+    <x:tableColumn id="5" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2674,238 +3046,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF24364B"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>Graph+ UI interaction matrix</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Review each worksheet, set Review decision, and add notes. Two-finger translation is one gesture regardless of whether it starts over a node or the background.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Permanent Graph Engine behavior contract. Code and regression tests must remain aligned with every approved row.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Worksheet</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>Rows</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>Review decision</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="str">
+      <x:c r="E5" s="99" t="str">
         <x:v>Reviewer notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>State Definitions</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Defines selection state, the calculated selection centroid, the stored camera focus point, camera actions, and deferred node-specific focus.</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="n">
+      <x:c r="B6" s="101" t="str">
+        <x:v>Canonical states, camera terms, and invariants</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>State Policies</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>State-owned camera, render, and primary navigation policy</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>State Transitions</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>All state-changing stationary activations</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="D8" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Focus Rendering</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Local render visibility and emphasis</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D9" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
         <x:v>Desktop Pointer</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Primary means left button. Secondary means right button or equivalent.</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="B10" s="101" t="str">
+        <x:v>Mouse and pointer matrix</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
         <x:v>Desktop Trackpad</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>A browser usually reports physical mouse-wheel and two-finger trackpad scroll through the same wheel event path.</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="n">
+      <x:c r="B11" s="105" t="str">
+        <x:v>Wheel, two-finger scroll, and pinch matrix</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>Keyboard and modifier matrix</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D12" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Mobile Touch</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>One-finger, tap, long-press, and double-tap matrix</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D13" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E13" s="105" t="str"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
+        <x:v>Mobile Two-Finger</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>Translation and pinch matrix</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D14" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
+        <x:v>Stylus</x:v>
+      </x:c>
+      <x:c r="B15" s="105" t="str">
+        <x:v>Direct pen pointer matrix</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D15" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E15" s="105" t="str"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="101" t="str">
+        <x:v>Centering</x:v>
+      </x:c>
+      <x:c r="B16" s="101" t="str">
+        <x:v>Center, Fit, and Focus zoom limits</x:v>
+      </x:c>
+      <x:c r="C16" s="101" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D16" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E16" s="101" t="str"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="105" t="str">
+        <x:v>Node Context Menu</x:v>
+      </x:c>
+      <x:c r="B17" s="105" t="str">
+        <x:v>Generic node context actions</x:v>
+      </x:c>
+      <x:c r="C17" s="105" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E17" s="105" t="str"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="101" t="str">
+        <x:v>Quick Settings UI</x:v>
+      </x:c>
+      <x:c r="B18" s="101" t="str">
+        <x:v>Panel input isolation</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D18" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E18" s="101" t="str">
+        <x:v>Unchanged by state formalization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="105" t="str">
+        <x:v>Quick Settings Controls</x:v>
+      </x:c>
+      <x:c r="B19" s="105" t="str">
+        <x:v>Profile-backed visibility</x:v>
+      </x:c>
+      <x:c r="C19" s="105" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D19" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E19" s="105" t="str">
+        <x:v>Unchanged by state formalization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="101" t="str">
+        <x:v>Note Preview</x:v>
+      </x:c>
+      <x:c r="B20" s="101" t="str">
+        <x:v>Cmd-hover desktop note preview</x:v>
+      </x:c>
+      <x:c r="C20" s="101" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Keyboard</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>This matrix applies on desktop and on mobile when a hardware keyboard is present. Ctrl edits selection; Option temporarily reveals selection neighbors and connecting links.</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>Mobile Touch</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Two-finger behavior is defined separately. One-finger background behavior remains open for review.</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>Mobile Two-Finger</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Starting over a node or the background is irrelevant. Moving both fingers together is translation; changing the distance between them is pinch zoom.</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Stylus</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Stylus behavior follows the direct non-mouse input path where the device supplies pointer events.</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Center + Fit</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Two ordered actions: center the camera on selected nodes, or the entire graph when nothing is selected, then separately fit zoom to that same target.</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="19" t="str">
-        <x:v>Node Context Menu</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="str">
-        <x:v>The menu opens from desktop secondary click or mobile and stylus long press. Node-specific Focus is deferred.</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="str"/>
-    </x:row>
-    <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>Quick Settings UI</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>Panel input must never leak into graph navigation behind the panel.</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str"/>
-    </x:row>
-    <x:row r="16" ht="43" customHeight="1">
-      <x:c r="A16" s="19" t="str">
-        <x:v>Quick Settings Controls</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="str">
-        <x:v>Visibility depends on the active Graph Engine profile and whether the view is Global Graph+ or Local Graph+.</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E16" s="19" t="str"/>
-    </x:row>
-    <x:row r="17" ht="43" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>Note Preview</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
-        <x:v>Preview is a desktop pointer feature triggered by Cmd-hover on a note node.</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D17" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="str"/>
-    </x:row>
-    <x:row r="18" ht="43" customHeight="1">
-      <x:c r="A18" s="19" t="str">
+      <x:c r="D20" s="103" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E20" s="101" t="str">
+        <x:v>Unchanged by state formalization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="105" t="str">
         <x:v>Open Decisions</x:v>
       </x:c>
-      <x:c r="B18" s="19" t="str">
-        <x:v>Resolved decisions from UI contract review.</x:v>
-      </x:c>
-      <x:c r="C18" s="19" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D18" s="20" t="str">
+      <x:c r="B21" s="105" t="str">
+        <x:v>Explicitly deferred follow-up design</x:v>
+      </x:c>
+      <x:c r="C21" s="105" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="103" t="str">
         <x:v>Approved</x:v>
       </x:c>
-      <x:c r="E18" s="19" t="str"/>
+      <x:c r="E21" s="105" t="str">
+        <x:v>No contract inconsistency remains</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D18">
@@ -2919,124 +3359,152 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd118e2cbf286437c"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
-        <x:v>Node context menu actions</x:v>
-      </x:c>
+      <x:c r="A2" s="84" t="str">
+        <x:v>Node context menu</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>The menu is currently opened by desktop secondary click and mobile or stylus long press on a node.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Desktop secondary click and mobile or stylus long press open the menu without changing state by themselves.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Action</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>Availability</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
-        <x:v>Open note or Open tag</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Invoke the node primary action</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>When registered for the node</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Focus node (deferred)</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Future design: allow a user-selected node to become the camera focus point within a selection. This behavior is not part of the current contract.</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Deferred pending design and playtesting</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="D5" s="99" t="str">
+        <x:v>Selection / Focus effect</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Open note / tag</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Invoke primary node action</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>When registered for node</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>No automatic state change</x:v>
+      </x:c>
+      <x:c r="E6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Focus node</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Enter Focus through the same session operation as click / tap</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>When selection is non-empty</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Does not change selection</x:v>
+      </x:c>
+      <x:c r="E7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
         <x:v>Mind map from here</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Set the node as Form root and enable Mind Map</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
+      <x:c r="B8" s="101" t="str">
+        <x:v>Set node as Form root and enable Mind Map</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
         <x:v>Policy-controlled</x:v>
       </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Pin node or Unpin node</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
+      <x:c r="D8" s="101" t="str">
+        <x:v>Product action</x:v>
+      </x:c>
+      <x:c r="E8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Pin / Unpin node</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
         <x:v>Toggle layout pinning</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="C9" s="105" t="str">
         <x:v>Policy-controlled</x:v>
       </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>Consumer-provided action</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Invoke the registered node action</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>When contributed</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
+      <x:c r="D9" s="105" t="str">
+        <x:v>No selection change</x:v>
+      </x:c>
+      <x:c r="E9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Dismiss</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Close menu</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Always</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="E10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D10">
@@ -3050,6 +3518,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4433e7ef8205426d"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -3072,11 +3543,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Quick Settings interaction</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
         <x:v>Panel input must never leak into graph navigation behind the panel.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
@@ -3112,9 +3601,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F6" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F6" s="19"/>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
       <x:c r="A7" s="18" t="str">
@@ -3130,9 +3619,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F7" s="18"/>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -3148,9 +3637,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F8" s="19"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -3166,9 +3655,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F9" s="18"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -3184,9 +3673,9 @@
         <x:v>Required isolation</x:v>
       </x:c>
       <x:c r="E10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F10" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F10" s="19"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -3202,9 +3691,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F11" s="18"/>
     </x:row>
     <x:row r="12" ht="43" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -3220,9 +3709,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F12" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F12" s="19"/>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -3238,9 +3727,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F13" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F13" s="18"/>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -3256,9 +3745,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E14" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F14" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F14" s="19"/>
     </x:row>
     <x:row r="15" ht="43" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -3274,9 +3763,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="E15" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="F15" s="18"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="E6:E15">
@@ -3315,11 +3804,26 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Quick Settings controls</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
         <x:v>Visibility depends on the active Graph Engine profile and whether the view is Global Graph+ or Local Graph+.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
@@ -3349,9 +3853,9 @@
         <x:v>Search and lens settings affect visible graph projection</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E6" s="19"/>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
       <x:c r="A7" s="18" t="str">
@@ -3364,9 +3868,9 @@
         <x:v>Mix of profile and session controls</x:v>
       </x:c>
       <x:c r="D7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E7" s="18"/>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -3379,9 +3883,9 @@
         <x:v>Profile settings</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E8" s="19"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -3394,9 +3898,9 @@
         <x:v>Profile settings</x:v>
       </x:c>
       <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E9" s="18"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -3409,9 +3913,9 @@
         <x:v>Profile settings; boundaries apply in 2D</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E10" s="19"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -3424,9 +3928,9 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="D11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E11" s="18"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D11">
@@ -3461,11 +3965,26 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Note preview inputs</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
         <x:v>Preview is a desktop pointer feature triggered by Cmd/Ctrl-hover on a note node.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
@@ -3495,9 +4014,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E6" s="19"/>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
       <x:c r="A7" s="18" t="str">
@@ -3510,9 +4029,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E7" s="18"/>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -3525,9 +4044,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E8" s="19"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -3540,9 +4059,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E9" s="18"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -3555,9 +4074,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E10" s="19"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -3570,9 +4089,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E11" s="18"/>
     </x:row>
     <x:row r="12" ht="43" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -3585,9 +4104,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E12" s="19"/>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -3600,9 +4119,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E13" s="18"/>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -3615,9 +4134,9 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="D14" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="str"/>
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E14" s="19"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D14">
@@ -3641,208 +4160,143 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FFB7791F"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="67" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="105" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
-        <x:v>Resolved interaction decisions</x:v>
-      </x:c>
+      <x:c r="A2" s="84" t="str">
+        <x:v>Deferred decisions</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Decisions approved during UI contract review.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
-        <x:v>Decision</x:v>
-      </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Current implementation</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>Approval question</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
-        <x:v>Desktop 3D trackpad in Overview</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Unmodified two-finger scroll</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Pan in 3D Overview.</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Desktop secondary drag in 2D</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Secondary-button drag</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Pan in 2D.</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
-        <x:v>Secondary click target split</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Node versus background</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Node input opens the context menu; background input runs Center + Fit on the selection, or the graph if there is no selection.</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
+      <x:c r="A3" s="85" t="str">
+        <x:v>No unresolved inconsistency remains in the implemented interaction contract.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
+        <x:v>Topic</x:v>
+      </x:c>
+      <x:c r="B5" s="99" t="str">
+        <x:v>Current decision</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Product-language aliases</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Keep Overview / Explore / Focus canonical. Kosmos / Constellation / Local aliases are deferred.</x:v>
+      </x:c>
+      <x:c r="C6" s="107" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Local Graph+</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>May later become a direct expression of Focus rather than a separate concept.</x:v>
+      </x:c>
+      <x:c r="C7" s="107" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Exportable state policies</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Keep policies fixed and internal for V1; consider consumer export/configuration later.</x:v>
+      </x:c>
+      <x:c r="C8" s="107" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Ordinary node click</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Existing selection</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Accumulate selection and recalculate its centroid without moving the stored focus point.</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>One-finger touch pan</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Selection and focus effect</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>Preserve selection. Pan translates the stored focus point and changes its offset from the calculated centroid; Rotate uses that stored point.</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>Two-finger pan</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Selection and focus effect</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>Preserve selection. Two-finger Pan translates the stored focus point and changes its offset from the calculated centroid.</x:v>
-      </x:c>
-      <x:c r="D11" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str"/>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
     </x:row>
     <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Ctrl release</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Conditional Center + Fit</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>Center + Fit only after an initial selection that began empty; otherwise no camera change.</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E12" s="19"/>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Camera focus-point lifecycle</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Stored focus point and calculated selection centroid</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Initial selection sets focus to its centroid. Later membership edits update the centroid without moving focus. Pan changes the offset. Secondary click resets focus to the current target centroid. Selected-node motion translates focus by the centroid delta to preserve the offset.</x:v>
-      </x:c>
-      <x:c r="D13" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str"/>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
     </x:row>
     <x:row r="14" ht="60" customHeight="1">
-      <x:c r="A14" s="43" t="str">
-        <x:v>Option neighbor highlight</x:v>
-      </x:c>
-      <x:c r="B14" s="43" t="str">
-        <x:v>Transient hover-equivalent presentation</x:v>
-      </x:c>
-      <x:c r="C14" s="43" t="str">
-        <x:v>While Option is held, highlight direct neighbors of the current selection and the links connecting them to the selection using the same treatment as hovering the selected node. Update the highlight as selection changes. On release, restore normal presentation without changing selection, focus, or camera.</x:v>
-      </x:c>
-      <x:c r="D14" s="78" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E14" s="43"/>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
     </x:row>
     <x:row r="15" ht="60" customHeight="1">
-      <x:c r="A15" s="43" t="str">
-        <x:v>Tag node selection</x:v>
-      </x:c>
-      <x:c r="B15" s="43" t="str">
-        <x:v>Same as ordinary node selection</x:v>
-      </x:c>
-      <x:c r="C15" s="43" t="str">
-        <x:v>Clicking a tag selects only that tag. Region members remain unselected and do not receive selected-label presentation.</x:v>
-      </x:c>
-      <x:c r="D15" s="80" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E15" s="43"/>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
     </x:row>
     <x:row r="16" ht="60" customHeight="1">
-      <x:c r="A16" s="43" t="str">
-        <x:v>Cmd-scroll</x:v>
-      </x:c>
-      <x:c r="B16" s="43" t="str">
-        <x:v>Ordinary wheel navigation</x:v>
-      </x:c>
-      <x:c r="C16" s="43" t="str">
-        <x:v>Cmd does not enable zoom. Cmd-scroll follows the same 2D and 3D navigation behavior as unmodified wheel input.</x:v>
-      </x:c>
-      <x:c r="D16" s="80" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E16" s="43"/>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D13">
@@ -3865,199 +4319,900 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a37b8e369f548e9"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF24384D"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="84" t="str">
+        <x:v>State-owned interaction policies</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
+      <x:c r="G2" s="84"/>
+      <x:c r="H2" s="84"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="85" t="str">
+        <x:v>The fixed internal V1 policy table consumed by input, camera, and Anima presentation.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+      <x:c r="H3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+      <x:c r="G4" s="83"/>
+      <x:c r="H4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="B5" s="99" t="str">
+        <x:v>Selection</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>Focused node</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="str">
+        <x:v>Camera target</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Center + Fit target</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Render scope</x:v>
+      </x:c>
+      <x:c r="G5" s="99" t="str">
+        <x:v>Primary 2D</x:v>
+      </x:c>
+      <x:c r="H5" s="99" t="str">
+        <x:v>Primary 3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Graph centroid</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str">
+        <x:v>Whole graph</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="str">
+        <x:v>Whole graph</x:v>
+      </x:c>
+      <x:c r="G6" s="101" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="H6" s="101" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>One or more</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Stored selection-centroid focus</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str">
+        <x:v>Selection</x:v>
+      </x:c>
+      <x:c r="F7" s="105" t="str">
+        <x:v>Graph with selection emphasis</x:v>
+      </x:c>
+      <x:c r="G7" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="H7" s="105" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>One or more</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>One node; membership independent</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Focused node</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>Focused node + immediate neighbors</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
+        <x:v>Focused local view</x:v>
+      </x:c>
+      <x:c r="G8" s="101" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="H8" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ff5286e68945e9"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF24384D"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="84" t="str">
+        <x:v>Overview / Explore / Focus transitions</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
+      <x:c r="G2" s="84"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Stationary activations change awareness state; crossed drag thresholds become navigation instead.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+      <x:c r="G4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
+        <x:v>From</x:v>
+      </x:c>
+      <x:c r="B5" s="99" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>Guard</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="str">
+        <x:v>To</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Selection effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Focus effect</x:v>
+      </x:c>
+      <x:c r="G5" s="99" t="str">
+        <x:v>Camera / action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Click / tap node</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Any visible node</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str">
+        <x:v>Select node</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="str">
+        <x:v>Focus clicked node</x:v>
+      </x:c>
+      <x:c r="G6" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Click unselected node</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str">
+        <x:v>Add node + shortest-path bridge</x:v>
+      </x:c>
+      <x:c r="F7" s="105" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="G7" s="105" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Click selected node</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>No change</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
+        <x:v>Focus clicked node</x:v>
+      </x:c>
+      <x:c r="G8" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Click / tap background</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="F9" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="G9" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Click different visible node</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>No change</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>Hop to clicked node</x:v>
+      </x:c>
+      <x:c r="G10" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Single click focused node</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>After double-click arbitration</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Focus or Overview</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>Toggle focused node</x:v>
+      </x:c>
+      <x:c r="F11" s="105" t="str">
+        <x:v>Retain unless selection becomes empty</x:v>
+      </x:c>
+      <x:c r="G11" s="105" t="str">
+        <x:v>Fit graph only if selection becomes empty</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>Click / tap background</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Two or more selected</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>Retain</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="G12" s="101" t="str">
+        <x:v>Center + Fit selection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Click / tap background</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>One selected</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="E13" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="F13" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="G13" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>Double-click / tap focused node</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>Focused before first activation</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str">
+        <x:v>No change</x:v>
+      </x:c>
+      <x:c r="F14" s="101" t="str">
+        <x:v>No change</x:v>
+      </x:c>
+      <x:c r="G14" s="101" t="str">
+        <x:v>Invoke primary node action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="B15" s="105" t="str">
+        <x:v>Escape</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D15" s="105" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="E15" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="F15" s="105" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="G15" s="105" t="str">
+        <x:v>No implicit fit</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d6d506f44244e33"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF24384D"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="84" t="str">
+        <x:v>Focus local rendering scope</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Focus keeps the constellation legible, grays the local neighborhood, and removes everything else.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
+        <x:v>Element</x:v>
+      </x:c>
+      <x:c r="B5" s="99" t="str">
+        <x:v>Node presentation</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>Label presentation</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="str">
+        <x:v>Link presentation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Selected constellation node</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Rendered and lit</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Selected label emphasis</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Selection-selected links lit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Focused node, selected</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Rendered and lit</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Normal local label policy</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Focus-neighbor links remain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Focused node, unselected</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Rendered gray; no focus-specific selection color</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Normal local label policy</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Focus-neighbor links gray unless selected-selected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Immediate neighbor, unselected</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Rendered gray</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Normal local label policy</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Link to focused node rendered gray</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Selected node outside immediate neighborhood</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Rendered and lit</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Selected label emphasis</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Selected-selected links remain</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>All other nodes and links</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Not rendered</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Hidden</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Hidden</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83262f55c73443cb"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="56" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>State and camera definitions</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>These terms are used consistently across the interaction tables.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Canonical terms shared by code, tests, and every interaction table.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Term</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>Definition</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>Contract significance</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="D5" s="99" t="str">
+        <x:v>Camera / render consequence</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Overview</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>No nodes are selected; the camera has no selection focus.</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Desktop trackpad scroll pans in 3D Overview.</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="B6" s="101" t="str">
+        <x:v>No selection and no focused node.</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Whole-graph awareness.</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Graph centroid / graph fit</x:v>
+      </x:c>
+      <x:c r="E6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
         <x:v>Explore</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>One or more nodes are selected.</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>The selection centroid is recalculated whenever membership or node positions change.</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="B7" s="105" t="str">
+        <x:v>One or more selected nodes and no focused node.</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Selected constellation awareness.</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Stored selection-centroid focus / selection fit</x:v>
+      </x:c>
+      <x:c r="E7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
         <x:v>Focus</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>The camera's stored focus point. An initial selection sets it to the calculated selection centroid.</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Later additive or subtractive selection edits recalculate the centroid without moving the focus point. Selected-node motion may translate the focus point by the centroid delta, preserving the current offset.</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Node-specific focus (deferred)</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>A future user-selected node could become a focus point within a selection.</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Not part of the current interaction contract; requires further design and playtesting.</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
+      <x:c r="B8" s="101" t="str">
+        <x:v>A non-empty selection plus one focused node.</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Local-node awareness. Focus does not imply that the focused node is selected.</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Focused node / focused neighborhood fit</x:v>
+      </x:c>
+      <x:c r="E8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Selection</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>The zero-or-more-node set chosen by the user or consumer.</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Drives constellation presentation.</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Empty selection invalidates Focus</x:v>
+      </x:c>
+      <x:c r="E9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Selection centroid</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Arithmetic mean of current selected-node positions.</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Recalculates after additive, subtractive, or positional changes.</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Explore motion follows centroid delta; membership edits do not auto-recenter</x:v>
+      </x:c>
+      <x:c r="E10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Focused node</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>The node actively tracked by the camera in Focus.</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>May remain focused after being removed from selection.</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Camera follows node motion</x:v>
+      </x:c>
+      <x:c r="E11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Translate camera position and focus point laterally through the scene.</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>Changes the offset between the stored focus point and the selection centroid without resetting camera angle.</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
+      <x:c r="B12" s="101" t="str">
+        <x:v>Translate camera position and target laterally.</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Changes framing without changing selection.</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Normal in Overview and 2D Explore</x:v>
+      </x:c>
+      <x:c r="E12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Temporary pan offset that springs back to the focused node.</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Communicates camera lock in 2D Focus.</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Focus only</x:v>
+      </x:c>
+      <x:c r="E13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
         <x:v>Rotate</x:v>
       </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Rotate camera around its stored focus point.</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>Changes angle without fitting or recentering the graph.</x:v>
-      </x:c>
-      <x:c r="D11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Zoom</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Change camera distance around an input anchor.</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>Does not invoke Center + Fit or reset orientation.</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
+      <x:c r="B14" s="101" t="str">
+        <x:v>Rotate camera around its current target.</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>Changes angle without fitting or recentering.</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>Default 3D Explore and Focus navigation</x:v>
+      </x:c>
+      <x:c r="E14" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="B15" s="105" t="str">
+        <x:v>Zoom from pointer or touch-centroid distance to the focused node.</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="str">
+        <x:v>Away zooms in; toward center zooms out.</x:v>
+      </x:c>
+      <x:c r="D15" s="105" t="str">
+        <x:v>Focus only</x:v>
+      </x:c>
+      <x:c r="E15" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="101" t="str">
         <x:v>Center</x:v>
       </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Translate the camera to the target centroid.</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>The target is the selected portion, or the whole graph when there is no selection. Center preserves angle, orientation, up vector, zoom, and distance.</x:v>
-      </x:c>
-      <x:c r="D13" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="19" t="str">
+      <x:c r="B16" s="101" t="str">
+        <x:v>Translate camera target to graph/selection centroid or focused node.</x:v>
+      </x:c>
+      <x:c r="C16" s="101" t="str">
+        <x:v>Preserves angle, orientation, up vector, zoom, and distance.</x:v>
+      </x:c>
+      <x:c r="D16" s="101" t="str">
+        <x:v>State-aware target</x:v>
+      </x:c>
+      <x:c r="E16" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="105" t="str">
         <x:v>Fit</x:v>
       </x:c>
-      <x:c r="B14" s="19" t="str">
-        <x:v>Adjust camera zoom to fit the target.</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="str">
-        <x:v>Does not change the target centroid, angle, orientation, or up vector.</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="str"/>
-    </x:row>
-    <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="71" t="str">
+      <x:c r="B17" s="105" t="str">
+        <x:v>Adjust zoom or camera distance to contain the target with padding.</x:v>
+      </x:c>
+      <x:c r="C17" s="105" t="str">
+        <x:v>Does not reset angle or up vector.</x:v>
+      </x:c>
+      <x:c r="D17" s="105" t="str">
+        <x:v>State-aware target</x:v>
+      </x:c>
+      <x:c r="E17" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="101" t="str">
         <x:v>Center + Fit</x:v>
       </x:c>
-      <x:c r="B15" s="71" t="str">
-        <x:v>First Center on the target, then Fit that same target.</x:v>
-      </x:c>
-      <x:c r="C15" s="71" t="str">
-        <x:v>Uses the selection as target, or the graph when there is no selection.</x:v>
-      </x:c>
-      <x:c r="D15" s="71" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="E15" s="71"/>
+      <x:c r="B18" s="101" t="str">
+        <x:v>Center first, then independently fit the same state target.</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="str">
+        <x:v>Overview targets graph; Explore selection; Focus local neighborhood.</x:v>
+      </x:c>
+      <x:c r="D18" s="101" t="str">
+        <x:v>Canonical recenter command</x:v>
+      </x:c>
+      <x:c r="E18" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D14">
@@ -4097,551 +5252,587 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dddb693191e419f"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="39" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="53" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>Desktop mouse and pointer inputs</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
+      <x:c r="G2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
+      <x:c r="A3" s="85" t="str">
         <x:v>Primary means left button. Secondary means right button or equivalent.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+      <x:c r="G4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Target or state</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
+        <x:v>Target / state</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
         <x:v>2D behavior</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>3D behavior</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Selection or focus effect</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="H5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="E5" s="99" t="str">
+        <x:v>Selection / Focus effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Camera effect</x:v>
+      </x:c>
+      <x:c r="G5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Hover</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
+      <x:c r="B6" s="101" t="str">
+        <x:v>Node / any state</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Highlight node</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Highlight node</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="str">
+        <x:v>Transient only</x:v>
+      </x:c>
+      <x:c r="G6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Cmd + hover</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Note node</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Open note preview</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Open note preview</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F7" s="105" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Background / Overview</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Activate background</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>Remain Overview</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Background / Explore</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Clear selection</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>Enter Overview</x:v>
+      </x:c>
+      <x:c r="F9" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+      <x:c r="G9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Background / Focus, 2+ selected</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Exit Focus</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Enter Explore</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>Center + Fit selection</x:v>
+      </x:c>
+      <x:c r="G10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Background / Focus, 1 selected</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Clear selection</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>Enter Overview</x:v>
+      </x:c>
+      <x:c r="F11" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+      <x:c r="G11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>Node / Overview</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Select + Focus</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>Enter Focus</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Unselected node / Explore</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Add node + path bridge</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E13" s="105" t="str">
+        <x:v>Remain Explore</x:v>
+      </x:c>
+      <x:c r="F13" s="105" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>Selected node / Explore</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>Enter Focus</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str">
+        <x:v>Selection unchanged</x:v>
+      </x:c>
+      <x:c r="F14" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G14" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B15" s="105" t="str">
+        <x:v>Different local node / Focus</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="str">
+        <x:v>Hop Focus</x:v>
+      </x:c>
+      <x:c r="D15" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E15" s="105" t="str">
+        <x:v>Selection unchanged</x:v>
+      </x:c>
+      <x:c r="F15" s="105" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G15" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="101" t="str">
+        <x:v>Primary click</x:v>
+      </x:c>
+      <x:c r="B16" s="101" t="str">
+        <x:v>Focused node / Focus</x:v>
+      </x:c>
+      <x:c r="C16" s="101" t="str">
+        <x:v>Toggle membership after double-click delay</x:v>
+      </x:c>
+      <x:c r="D16" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E16" s="101" t="str">
+        <x:v>Focus independent of membership</x:v>
+      </x:c>
+      <x:c r="F16" s="101" t="str">
+        <x:v>Graph fit only if selection empties</x:v>
+      </x:c>
+      <x:c r="G16" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="105" t="str">
+        <x:v>Double click</x:v>
+      </x:c>
+      <x:c r="B17" s="105" t="str">
+        <x:v>Already-focused node</x:v>
+      </x:c>
+      <x:c r="C17" s="105" t="str">
+        <x:v>Primary node action</x:v>
+      </x:c>
+      <x:c r="D17" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E17" s="105" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F17" s="105" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G17" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="101" t="str">
+        <x:v>Ctrl + click</x:v>
+      </x:c>
+      <x:c r="B18" s="101" t="str">
         <x:v>Node</x:v>
       </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Highlight node</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="str">
-        <x:v>Highlight node</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str">
+      <x:c r="C18" s="101" t="str">
+        <x:v>Add / remove selection</x:v>
+      </x:c>
+      <x:c r="D18" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E18" s="101" t="str">
+        <x:v>Focus remains valid while selection non-empty</x:v>
+      </x:c>
+      <x:c r="F18" s="101" t="str">
+        <x:v>No camera change while held</x:v>
+      </x:c>
+      <x:c r="G18" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="105" t="str">
+        <x:v>Primary drag</x:v>
+      </x:c>
+      <x:c r="B19" s="105" t="str">
+        <x:v>Background / Overview</x:v>
+      </x:c>
+      <x:c r="C19" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="D19" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="E19" s="105" t="str">
         <x:v>No state change</x:v>
       </x:c>
-      <x:c r="F6" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H6" s="19"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Hover</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Background</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Clear hover</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Clear hover</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
+      <x:c r="F19" s="105" t="str">
+        <x:v>Translate camera</x:v>
+      </x:c>
+      <x:c r="G19" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="101" t="str">
+        <x:v>Primary drag</x:v>
+      </x:c>
+      <x:c r="B20" s="101" t="str">
+        <x:v>Background / Explore</x:v>
+      </x:c>
+      <x:c r="C20" s="101" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="D20" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E20" s="101" t="str">
+        <x:v>Retain selection</x:v>
+      </x:c>
+      <x:c r="F20" s="101" t="str">
+        <x:v>State-owned navigation</x:v>
+      </x:c>
+      <x:c r="G20" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="105" t="str">
+        <x:v>Primary drag</x:v>
+      </x:c>
+      <x:c r="B21" s="105" t="str">
+        <x:v>Selected node / Overview or Explore</x:v>
+      </x:c>
+      <x:c r="C21" s="105" t="str">
+        <x:v>Drag node</x:v>
+      </x:c>
+      <x:c r="D21" s="105" t="str">
+        <x:v>Drag node</x:v>
+      </x:c>
+      <x:c r="E21" s="105" t="str">
+        <x:v>Selection centroid moves</x:v>
+      </x:c>
+      <x:c r="F21" s="105" t="str">
+        <x:v>Explore follows centroid delta</x:v>
+      </x:c>
+      <x:c r="G21" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="101" t="str">
+        <x:v>Primary drag</x:v>
+      </x:c>
+      <x:c r="B22" s="101" t="str">
+        <x:v>Any target / Focus</x:v>
+      </x:c>
+      <x:c r="C22" s="101" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="D22" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E22" s="101" t="str">
+        <x:v>No selection change</x:v>
+      </x:c>
+      <x:c r="F22" s="101" t="str">
+        <x:v>Camera remains locked to focus</x:v>
+      </x:c>
+      <x:c r="G22" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H22"/>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="105" t="str">
+        <x:v>Secondary click</x:v>
+      </x:c>
+      <x:c r="B23" s="105" t="str">
+        <x:v>Background / any state</x:v>
+      </x:c>
+      <x:c r="C23" s="105" t="str">
+        <x:v>Center + Fit state target</x:v>
+      </x:c>
+      <x:c r="D23" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E23" s="105" t="str">
+        <x:v>No selection change</x:v>
+      </x:c>
+      <x:c r="F23" s="105" t="str">
+        <x:v>Graph / selection / local target</x:v>
+      </x:c>
+      <x:c r="G23" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H23"/>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="101" t="str">
+        <x:v>Secondary click</x:v>
+      </x:c>
+      <x:c r="B24" s="101" t="str">
+        <x:v>Node</x:v>
+      </x:c>
+      <x:c r="C24" s="101" t="str">
+        <x:v>Open context menu</x:v>
+      </x:c>
+      <x:c r="D24" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E24" s="101" t="str">
+        <x:v>No automatic state change</x:v>
+      </x:c>
+      <x:c r="F24" s="101" t="str">
+        <x:v>No automatic camera change</x:v>
+      </x:c>
+      <x:c r="G24" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H24"/>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="105" t="str">
+        <x:v>Secondary drag</x:v>
+      </x:c>
+      <x:c r="B25" s="105" t="str">
+        <x:v>Overview or Explore</x:v>
+      </x:c>
+      <x:c r="C25" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="D25" s="105" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E25" s="105" t="str">
         <x:v>No state change</x:v>
       </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H7" s="18"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
-        <x:v>Cmd + hover</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Note node</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Open note preview</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="str">
-        <x:v>Open note preview</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str">
-        <x:v>No selection change</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H8" s="19"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Cmd release or pointer leave</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Preview trigger</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Dismiss after handoff delay</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>No selection change</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H9" s="18"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>Primary click</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Background</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>Clear selection; camera focus ends</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str">
-        <x:v>Emit background activation</x:v>
-      </x:c>
-      <x:c r="F10" s="19" t="str">
-        <x:v>Verify</x:v>
-      </x:c>
-      <x:c r="G10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H10" s="19"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>Primary click</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Node, including tag, with no existing selection</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>On release, select only the clicked node; then Center + Fit selection</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str">
-        <x:v>Begin selection with only the clicked node; set focus point to the calculated selection centroid</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H11" s="18"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Primary click</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Node, including tag, with an existing selection</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>On release, add the clicked node and shortest-path bridge; no camera change</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str">
-        <x:v>Accumulate the clicked node and bridge; recalculate the centroid; keep the existing focus point</x:v>
-      </x:c>
-      <x:c r="F12" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G12" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H12" s="19"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Primary click</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Already-selected node</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Open note or tag</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Retain selection and the existing stored focus point</x:v>
-      </x:c>
-      <x:c r="F13" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H13" s="18"/>
-    </x:row>
-    <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="19" t="str">
-        <x:v>Ctrl + primary click</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="str">
-        <x:v>Unselected node, while Ctrl is held</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="str">
-        <x:v>Add node to selection; no camera change yet</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="str">
-        <x:v>Update selection and centroid without moving focus</x:v>
-      </x:c>
-      <x:c r="F14" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G14" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H14" s="19"/>
-    </x:row>
-    <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>Ctrl + primary click</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>Selected node, while Ctrl is held</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Remove node from selection; no camera change yet</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Update selection and centroid without moving focus</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G15" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H15" s="18"/>
-    </x:row>
-    <x:row r="16" ht="43" customHeight="1">
-      <x:c r="A16" s="19" t="str">
-        <x:v>Ctrl release</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="str">
-        <x:v>Selection began with no selected nodes</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="str">
-        <x:v>Center + Fit resulting selection</x:v>
-      </x:c>
-      <x:c r="D16" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E16" s="19" t="str">
-        <x:v>Keep resulting selection; set focus to its centroid</x:v>
-      </x:c>
-      <x:c r="F16" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G16" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H16" s="19"/>
-    </x:row>
-    <x:row r="17" ht="43" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>Ctrl release</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
-        <x:v>Selection existed before Ctrl was held</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>No camera change</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="str">
-        <x:v>Keep additions and removals; keep the existing focus point</x:v>
-      </x:c>
-      <x:c r="F17" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G17" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H17" s="18"/>
-    </x:row>
-    <x:row r="18" ht="43" customHeight="1">
-      <x:c r="A18" s="19" t="str">
-        <x:v>Primary drag</x:v>
-      </x:c>
-      <x:c r="B18" s="19" t="str">
-        <x:v>Background, no selection</x:v>
-      </x:c>
-      <x:c r="C18" s="19" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="E18" s="19" t="str">
-        <x:v>No selection change; pan translates the stored focus point</x:v>
-      </x:c>
-      <x:c r="F18" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G18" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H18" s="19"/>
-    </x:row>
-    <x:row r="19" ht="43" customHeight="1">
-      <x:c r="A19" s="18" t="str">
-        <x:v>Primary drag</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="str">
-        <x:v>Background, selection exists</x:v>
-      </x:c>
-      <x:c r="C19" s="18" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="E19" s="18" t="str">
-        <x:v>Preserve selection; pan changes its offset from the stored focus point</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G19" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H19" s="18"/>
-    </x:row>
-    <x:row r="20" ht="43" customHeight="1">
-      <x:c r="A20" s="19" t="str">
-        <x:v>Primary drag</x:v>
-      </x:c>
-      <x:c r="B20" s="19" t="str">
-        <x:v>Selected node</x:v>
-      </x:c>
-      <x:c r="C20" s="19" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="D20" s="19" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="E20" s="19" t="str">
-        <x:v>Selection centroid moves; translate focus point by the same delta to preserve the offset without refitting</x:v>
-      </x:c>
-      <x:c r="F20" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G20" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H20" s="19"/>
-    </x:row>
-    <x:row r="21" ht="43" customHeight="1">
-      <x:c r="A21" s="18" t="str">
-        <x:v>Primary drag</x:v>
-      </x:c>
-      <x:c r="B21" s="18" t="str">
-        <x:v>Unselected node outside selection</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="E21" s="18" t="str">
-        <x:v>Preserve selection; pan changes its offset from the stored focus point</x:v>
-      </x:c>
-      <x:c r="F21" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G21" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H21" s="18"/>
-    </x:row>
-    <x:row r="22" ht="43" customHeight="1">
-      <x:c r="A22" s="19" t="str">
-        <x:v>Secondary click</x:v>
-      </x:c>
-      <x:c r="B22" s="19" t="str">
-        <x:v>Background</x:v>
-      </x:c>
-      <x:c r="C22" s="19" t="str">
-        <x:v>Center + Fit selection, or graph if no selection</x:v>
-      </x:c>
-      <x:c r="D22" s="19" t="str">
-        <x:v>Center + Fit selection, or graph if no selection</x:v>
-      </x:c>
-      <x:c r="E22" s="19" t="str">
-        <x:v>Set focus point to the current target centroid, clearing any pan offset</x:v>
-      </x:c>
-      <x:c r="F22" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G22" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H22" s="19"/>
-    </x:row>
-    <x:row r="23" ht="43" customHeight="1">
-      <x:c r="A23" s="18" t="str">
-        <x:v>Secondary click</x:v>
-      </x:c>
-      <x:c r="B23" s="18" t="str">
-        <x:v>Node</x:v>
-      </x:c>
-      <x:c r="C23" s="18" t="str">
-        <x:v>Open node context menu</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E23" s="18" t="str">
-        <x:v>No state change until a menu action</x:v>
-      </x:c>
-      <x:c r="F23" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G23" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H23" s="18"/>
-    </x:row>
-    <x:row r="24" ht="43" customHeight="1">
-      <x:c r="A24" s="70" t="str">
+      <x:c r="F25" s="105" t="str">
+        <x:v>State-owned navigation</x:v>
+      </x:c>
+      <x:c r="G25" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H25"/>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="101" t="str">
         <x:v>Secondary drag</x:v>
       </x:c>
-      <x:c r="B24" s="70" t="str">
-        <x:v>Background or node</x:v>
-      </x:c>
-      <x:c r="C24" s="70" t="str">
-        <x:v>Pan</x:v>
-      </x:c>
-      <x:c r="D24" s="70" t="str">
-        <x:v>Rotate</x:v>
-      </x:c>
-      <x:c r="E24" s="70" t="str">
-        <x:v>Preserve selection; pan changes the focus-point offset and rotate uses the stored focus point</x:v>
-      </x:c>
-      <x:c r="F24" s="70" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G24" s="70" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H24" s="70"/>
-    </x:row>
-    <x:row r="25" ht="43" customHeight="1">
-      <x:c r="A25" s="71" t="str">
-        <x:v>Pointer cancel</x:v>
-      </x:c>
-      <x:c r="B25" s="71" t="str">
-        <x:v>Active pointer gesture</x:v>
-      </x:c>
-      <x:c r="C25" s="71" t="str">
-        <x:v>End gesture safely</x:v>
-      </x:c>
-      <x:c r="D25" s="71" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E25" s="71" t="str">
-        <x:v>Clear transient pointer state only</x:v>
-      </x:c>
-      <x:c r="F25" s="73" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G25" s="71" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H25" s="71"/>
-    </x:row>
-    <x:row r="26" ht="43" customHeight="1">
-      <x:c r="A26" s="70"/>
-      <x:c r="B26" s="70"/>
-      <x:c r="C26" s="70"/>
-      <x:c r="D26" s="70"/>
-      <x:c r="E26" s="70"/>
-      <x:c r="F26" s="70"/>
-      <x:c r="G26" s="70"/>
-      <x:c r="H26" s="70"/>
+      <x:c r="B26" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C26" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="D26" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="E26" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F26" s="101" t="str">
+        <x:v>Away in; toward center out</x:v>
+      </x:c>
+      <x:c r="G26" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H26"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G6:G23">
@@ -4691,246 +5882,253 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7be154686bda4921"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>Desktop trackpad and wheel inputs</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>A browser usually reports physical mouse-wheel and two-finger trackpad scroll through the same wheel event path.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Browser wheel events represent both physical wheels and trackpad translation; Ctrl identifies pinch-style zoom.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>State</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
+        <x:v>State / target</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
         <x:v>2D behavior</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>3D behavior</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="G5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
-        <x:v>Two-finger scroll or wheel</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Overview: no selected nodes</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
+      <x:c r="E5" s="99" t="str">
+        <x:v>State / camera effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Two-finger scroll / wheel</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="str">
+      <x:c r="D6" s="101" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="str">
-        <x:v>Verify 3D Overview behavior</x:v>
-      </x:c>
-      <x:c r="F6" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Two-finger scroll or wheel</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Explore: one or more selected nodes</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="E6" s="101" t="str">
+        <x:v>State unchanged</x:v>
+      </x:c>
+      <x:c r="F6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Two-finger scroll / wheel</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="D7" s="18" t="str">
+      <x:c r="D7" s="105" t="str">
         <x:v>Rotate</x:v>
       </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Intended rotation path</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
-        <x:v>Shift + two-finger scroll</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="str">
+      <x:c r="E7" s="105" t="str">
+        <x:v>Selection retained</x:v>
+      </x:c>
+      <x:c r="F7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Two-finger scroll / wheel</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>Camera remains focused</x:v>
+      </x:c>
+      <x:c r="F8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Trackpad pinch / Ctrl-wheel</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Zoom around pointer</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Zoom around pointer</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>State unchanged</x:v>
+      </x:c>
+      <x:c r="F9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Trackpad pinch / Ctrl-wheel</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Zoom around pointer</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Zoom around pointer</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Selection retained</x:v>
+      </x:c>
+      <x:c r="F10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Trackpad pinch / Ctrl-wheel</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Zoom around focused target</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Zoom around focused target</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>Focus zoom-out limit applies</x:v>
+      </x:c>
+      <x:c r="F11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Cmd + scroll / wheel</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
         <x:v>Any</x:v>
       </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Same as unmodified</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="str">
-        <x:v>Same as unmodified</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str">
-        <x:v>No dedicated modifier behavior</x:v>
-      </x:c>
-      <x:c r="F8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Trackpad pinch</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Any</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Zoom around gesture position</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
+      <x:c r="C12" s="101" t="str">
+        <x:v>Same as unmodified state navigation</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Same as unmodified state navigation</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>Never enables zoom</x:v>
+      </x:c>
+      <x:c r="F12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Wheel</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Quick Settings / note preview</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Scroll owning surface only</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>Ctrl + wheel</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Any</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>Zoom around pointer</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="str">
-        <x:v>Zoom around pointer</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G10" s="19" t="str"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
-        <x:v>Ctrl-generated pinch momentum</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Any</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>Continue bounded decaying zoom</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Wheel over Quick Settings</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Panel</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>Scroll panel only</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str">
-        <x:v>Must not move graph</x:v>
-      </x:c>
-      <x:c r="F12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G12" s="19" t="str"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Wheel over note preview</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Preview card</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Scroll preview only</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Must not move graph</x:v>
-      </x:c>
-      <x:c r="F13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G13" s="18" t="str"/>
+      <x:c r="E13" s="105" t="str">
+        <x:v>Must not leak to graph</x:v>
+      </x:c>
+      <x:c r="F13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G13"/>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="43" t="str">
-        <x:v>Cmd + two-finger scroll or wheel</x:v>
-      </x:c>
-      <x:c r="B14" s="43" t="str">
-        <x:v>Any</x:v>
-      </x:c>
-      <x:c r="C14" s="43" t="str">
-        <x:v>Same as unmodified</x:v>
-      </x:c>
-      <x:c r="D14" s="43" t="str">
-        <x:v>Same as unmodified</x:v>
-      </x:c>
-      <x:c r="E14" s="43" t="str">
-        <x:v>Cmd does not enable zoom</x:v>
-      </x:c>
-      <x:c r="F14" s="80" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G14" s="43"/>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F6:F13">
@@ -4951,351 +6149,307 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reded927e8614411e"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
-        <x:v>Keyboard inputs</x:v>
-      </x:c>
+      <x:c r="A2" s="84" t="str">
+        <x:v>Keyboard and modifier inputs</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>This matrix applies on desktop and on mobile when a hardware keyboard is present.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Applies on desktop and on mobile when a hardware keyboard is present.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
         <x:v>2D behavior</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="99" t="str">
         <x:v>3D behavior</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>State effect</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="G5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="D5" s="99" t="str">
+        <x:v>State / camera effect</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Arrow keys</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Pan by fixed step</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Pan by fixed step</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="str">
-        <x:v>Preserve selection; translate the stored focus point and change its centroid offset</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="B6" s="101" t="str">
+        <x:v>Pan fixed step</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Pan fixed step</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Preserve state</x:v>
+      </x:c>
+      <x:c r="E6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
         <x:v>Shift + arrows</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
+      <x:c r="B7" s="105" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="C7" s="105" t="str">
         <x:v>Rotate</x:v>
       </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Preserve selection; Pan changes the focus-point offset and Rotate uses the stored focus point</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="D7" s="105" t="str">
+        <x:v>Preserve state</x:v>
+      </x:c>
+      <x:c r="E7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
         <x:v>+ or =</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
+      <x:c r="B8" s="101" t="str">
         <x:v>Zoom in</x:v>
       </x:c>
-      <x:c r="C8" s="19" t="str">
+      <x:c r="C8" s="101" t="str">
         <x:v>Zoom in</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="str">
-        <x:v>Preserve camera angle</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
+      <x:c r="D8" s="101" t="str">
+        <x:v>Preserve target</x:v>
+      </x:c>
+      <x:c r="E8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
         <x:v>- or _</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="str">
+      <x:c r="B9" s="105" t="str">
         <x:v>Zoom out</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="C9" s="105" t="str">
         <x:v>Zoom out</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Preserve camera angle</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
+      <x:c r="D9" s="105" t="str">
+        <x:v>Focus zoom-out limit applies</x:v>
+      </x:c>
+      <x:c r="E9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Hold Ctrl + node clicks</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Edit selection</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>No camera change during edits</x:v>
+      </x:c>
+      <x:c r="E10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Release Ctrl after initial selection</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Center + Fit result</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Use resulting state target</x:v>
+      </x:c>
+      <x:c r="E11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Release Ctrl after existing-selection edits</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Retain changes and Focus</x:v>
+      </x:c>
+      <x:c r="E12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Hold Option</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Reveal neighbors + connecting links</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Transient; no selection or camera change</x:v>
+      </x:c>
+      <x:c r="E13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
+        <x:v>Hold Space</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>Suspend ordinary selection dimming</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>Transient only</x:v>
+      </x:c>
+      <x:c r="E14" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
         <x:v>Enter</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Open sole selected node</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
+      <x:c r="B15" s="105" t="str">
+        <x:v>Primary action when exactly one node selected</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="str">
-        <x:v>No action unless exactly one node is selected</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G10" s="19" t="str"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
+      <x:c r="D15" s="105" t="str">
+        <x:v>No generic fallback</x:v>
+      </x:c>
+      <x:c r="E15" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="101" t="str">
         <x:v>Escape</x:v>
       </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Clear selection; camera focus ends</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
+      <x:c r="B16" s="101" t="str">
+        <x:v>Clear selection and Focus</x:v>
+      </x:c>
+      <x:c r="C16" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Also dismiss note preview</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>Hold Space</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Temporarily remove selection dimming</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="str">
-        <x:v>Do not mutate selection</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G12" s="19" t="str"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Hold Ctrl</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Enable additive or removal selection</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
-        <x:v>Do not change presentation or camera while held; additions and removals recalculate the centroid without moving focus</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F13" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G13" s="18"/>
-    </x:row>
-    <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="19" t="str">
-        <x:v>Hold Option</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="str">
-        <x:v>Highlight direct neighbors of the current selection and the links connecting them to the selection</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="str">
-        <x:v>Use the same highlight treatment as hovering the selected node; do not mutate selection, focus, or camera; release restores normal selection presentation</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F14" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G14" s="19"/>
-    </x:row>
-    <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>Release Ctrl after editing an existing selection</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>No camera change</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>No camera change</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Keep additions and removals; recalculate the centroid without moving focus</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F15" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G15" s="18"/>
-    </x:row>
-    <x:row r="16" ht="43" customHeight="1">
-      <x:c r="A16" s="19" t="str">
-        <x:v>Release Ctrl after initial selection</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="str">
-        <x:v>Center + Fit</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="str">
-        <x:v>Center + Fit</x:v>
-      </x:c>
-      <x:c r="D16" s="19" t="str">
-        <x:v>Keep resulting selection; set focus to its centroid</x:v>
-      </x:c>
-      <x:c r="E16" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F16" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G16" s="19"/>
+      <x:c r="D16" s="101" t="str">
+        <x:v>Enter Overview</x:v>
+      </x:c>
+      <x:c r="E16" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
     </x:row>
     <x:row r="17" ht="43" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>Tab on graph or background</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
-        <x:v>Toggle Quick Settings</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
-        <x:v>Disabled while typing in a control</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F17" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G17" s="18"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
     </x:row>
     <x:row r="18" ht="43" customHeight="1">
-      <x:c r="A18" s="19" t="str">
-        <x:v>Shift + Tab</x:v>
-      </x:c>
-      <x:c r="B18" s="19" t="str">
-        <x:v>Normal reverse focus navigation</x:v>
-      </x:c>
-      <x:c r="C18" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="str">
-        <x:v>Do not toggle panel</x:v>
-      </x:c>
-      <x:c r="E18" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F18" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G18" s="19"/>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
     </x:row>
     <x:row r="19" ht="43" customHeight="1">
-      <x:c r="A19" s="43" t="str">
-        <x:v>0 or F</x:v>
-      </x:c>
-      <x:c r="B19" s="43" t="str">
-        <x:v>No graph action</x:v>
-      </x:c>
-      <x:c r="C19" s="43" t="str">
-        <x:v>No graph action</x:v>
-      </x:c>
-      <x:c r="D19" s="43" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="E19" s="43" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F19" s="76" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="G19" s="43"/>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F6:F18">
@@ -5316,421 +6470,512 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05cc6e7d69be4db8"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="39" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="37" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="37" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="39" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="43" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>Mobile touch inputs</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
+      <x:c r="G2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Two-finger behavior is defined separately. One-finger background drag pans in 2D and rotates the camera in 3D.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>One finger owns navigation. Mobile node movement is not bound to one-finger drag.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+      <x:c r="G3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+      <x:c r="G4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Target or state</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
+        <x:v>Target / state</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
         <x:v>2D behavior</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>3D behavior</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Selection or focus effect</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="H5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="E5" s="99" t="str">
+        <x:v>Selection / Focus effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Camera / action</x:v>
+      </x:c>
+      <x:c r="G5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Tap</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Background</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Clear selection; camera focus ends</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="str">
+      <x:c r="B6" s="101" t="str">
+        <x:v>Background / Overview</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Activate background</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="str">
-        <x:v>Activate background after double-tap arbitration</x:v>
-      </x:c>
-      <x:c r="F6" s="19" t="str">
-        <x:v>Verify</x:v>
-      </x:c>
-      <x:c r="G6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="E6" s="101" t="str">
+        <x:v>Remain Overview</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
         <x:v>Tap</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Node, no existing selection</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>On tap release, add or select node</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
+      <x:c r="B7" s="105" t="str">
+        <x:v>Background / Explore</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Clear selection</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Selection begins; set focus point to its calculated centroid</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>Verify</x:v>
-      </x:c>
-      <x:c r="G7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="E7" s="105" t="str">
+        <x:v>Enter Overview</x:v>
+      </x:c>
+      <x:c r="F7" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+      <x:c r="G7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
         <x:v>Tap</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Already-selected node</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>On tap release, open note or tag</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="str">
+      <x:c r="B8" s="101" t="str">
+        <x:v>Background / Focus, 2+ selected</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Exit Focus</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="str">
-        <x:v>Retain selection and the existing stored focus point</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
+      <x:c r="E8" s="101" t="str">
+        <x:v>Enter Explore</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
+        <x:v>Center + Fit selection</x:v>
+      </x:c>
+      <x:c r="G8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Background / Focus, 1 selected</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Clear selection</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>Enter Overview</x:v>
+      </x:c>
+      <x:c r="F9" s="105" t="str">
+        <x:v>Center + Fit graph</x:v>
+      </x:c>
+      <x:c r="G9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Node / Overview</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Select + Focus on release</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Enter Focus</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Selected node / Explore</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Enter Focus</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>Selection unchanged</x:v>
+      </x:c>
+      <x:c r="F11" s="105" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>Different local node / Focus</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Hop Focus</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>Selection unchanged</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>Center node; fit immediate neighbors</x:v>
+      </x:c>
+      <x:c r="G12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Focused node / Focus</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Toggle membership after double-tap delay</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E13" s="105" t="str">
+        <x:v>Focus independent of membership</x:v>
+      </x:c>
+      <x:c r="F13" s="105" t="str">
+        <x:v>Graph fit only if selection empties</x:v>
+      </x:c>
+      <x:c r="G13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="101" t="str">
         <x:v>One-finger drag</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Background, no selection</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="B14" s="101" t="str">
+        <x:v>Any target / Overview</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>Rotate camera</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>No selection change; 2D pan translates the stored focus point and 3D rotate uses it</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
+      <x:c r="D14" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str">
+        <x:v>No selection or node drag</x:v>
+      </x:c>
+      <x:c r="F14" s="101" t="str">
+        <x:v>Navigate</x:v>
+      </x:c>
+      <x:c r="G14" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="105" t="str">
         <x:v>One-finger drag</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Background, selection exists</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
+      <x:c r="B15" s="105" t="str">
+        <x:v>Any target / Explore</x:v>
+      </x:c>
+      <x:c r="C15" s="105" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="str">
+      <x:c r="D15" s="105" t="str">
         <x:v>Rotate</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="str">
-        <x:v>Preserve selection; navigation changes or uses the stored focus-point offset</x:v>
-      </x:c>
-      <x:c r="F10" s="19" t="str">
-        <x:v>Verify</x:v>
-      </x:c>
-      <x:c r="G10" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="H10" s="19" t="str"/>
-    </x:row>
-    <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="18" t="str">
+      <x:c r="E15" s="105" t="str">
+        <x:v>Selection retained; no node drag</x:v>
+      </x:c>
+      <x:c r="F15" s="105" t="str">
+        <x:v>Navigate</x:v>
+      </x:c>
+      <x:c r="G15" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="101" t="str">
         <x:v>One-finger drag</x:v>
       </x:c>
-      <x:c r="B11" s="18" t="str">
-        <x:v>Node, no existing selection</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="str">
-        <x:v>Node becomes sole selection; set focus point to its calculated centroid</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G11" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="43" customHeight="1">
-      <x:c r="A12" s="19" t="str">
-        <x:v>One-finger drag</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="str">
-        <x:v>Selected node</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="str">
-        <x:v>Drag node</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="str">
-        <x:v>Selection centroid moves; translate focus point by the same delta to preserve the offset without refitting</x:v>
-      </x:c>
-      <x:c r="F12" s="19" t="str">
-        <x:v>Verify</x:v>
-      </x:c>
-      <x:c r="G12" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H12" s="19" t="str"/>
-    </x:row>
-    <x:row r="13" ht="43" customHeight="1">
-      <x:c r="A13" s="18" t="str">
-        <x:v>Two-finger pinch</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>Zoom around gesture centroid</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="str">
+      <x:c r="B16" s="101" t="str">
+        <x:v>Any target / Focus</x:v>
+      </x:c>
+      <x:c r="C16" s="101" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="D16" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E16" s="101" t="str">
+        <x:v>State retained</x:v>
+      </x:c>
+      <x:c r="F16" s="101" t="str">
+        <x:v>Camera remains locked to focus</x:v>
+      </x:c>
+      <x:c r="G16" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H16"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="105" t="str">
+        <x:v>Double tap</x:v>
+      </x:c>
+      <x:c r="B17" s="105" t="str">
+        <x:v>Background / any state</x:v>
+      </x:c>
+      <x:c r="C17" s="105" t="str">
+        <x:v>Center + Fit state target</x:v>
+      </x:c>
+      <x:c r="D17" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Pinch takes priority over translation</x:v>
-      </x:c>
-      <x:c r="F13" s="18" t="str">
-        <x:v>Confirmed gesture</x:v>
-      </x:c>
-      <x:c r="G13" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14" ht="43" customHeight="1">
-      <x:c r="A14" s="19" t="str">
-        <x:v>Translation changing into pinch</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="str">
-        <x:v>Switch to zoom after distance threshold</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="str">
+      <x:c r="E17" s="105" t="str">
+        <x:v>No selection change</x:v>
+      </x:c>
+      <x:c r="F17" s="105" t="str">
+        <x:v>Graph / selection / local target</x:v>
+      </x:c>
+      <x:c r="G17" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H17"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="101" t="str">
+        <x:v>Double tap</x:v>
+      </x:c>
+      <x:c r="B18" s="101" t="str">
+        <x:v>Already-focused node</x:v>
+      </x:c>
+      <x:c r="C18" s="101" t="str">
+        <x:v>Primary node action</x:v>
+      </x:c>
+      <x:c r="D18" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E14" s="19" t="str">
-        <x:v>Avoid permanent gesture misclassification</x:v>
-      </x:c>
-      <x:c r="F14" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G14" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H14" s="19" t="str"/>
-    </x:row>
-    <x:row r="15" ht="43" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>Double-tap; hold second tap; drag vertically</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Precision zoom</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
+      <x:c r="E18" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F18" s="101" t="str">
+        <x:v>No camera change</x:v>
+      </x:c>
+      <x:c r="G18" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H18"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="105" t="str">
+        <x:v>Double-tap drag</x:v>
+      </x:c>
+      <x:c r="B19" s="105" t="str">
+        <x:v>Overview or Explore</x:v>
+      </x:c>
+      <x:c r="C19" s="105" t="str">
+        <x:v>Vertical zoom</x:v>
+      </x:c>
+      <x:c r="D19" s="105" t="str">
+        <x:v>Horizontal rotate + vertical zoom</x:v>
+      </x:c>
+      <x:c r="E19" s="105" t="str">
+        <x:v>State retained</x:v>
+      </x:c>
+      <x:c r="F19" s="105" t="str">
+        <x:v>Continuous combined control</x:v>
+      </x:c>
+      <x:c r="G19" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H19"/>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="101" t="str">
+        <x:v>Double-tap drag</x:v>
+      </x:c>
+      <x:c r="B20" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C20" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="D20" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="E20" s="101" t="str">
+        <x:v>State retained</x:v>
+      </x:c>
+      <x:c r="F20" s="101" t="str">
+        <x:v>Away in; toward center out</x:v>
+      </x:c>
+      <x:c r="G20" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H20"/>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="105" t="str">
+        <x:v>Long press</x:v>
+      </x:c>
+      <x:c r="B21" s="105" t="str">
+        <x:v>Background / any state</x:v>
+      </x:c>
+      <x:c r="C21" s="105" t="str">
+        <x:v>Center + Fit state target</x:v>
+      </x:c>
+      <x:c r="D21" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Anchor at second-tap position</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G15" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H15" s="18" t="str"/>
-    </x:row>
-    <x:row r="16" ht="43" customHeight="1">
-      <x:c r="A16" s="19" t="str">
-        <x:v>Long press about 450 ms</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="str">
-        <x:v>Background</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="str">
-        <x:v>Center + Fit selection, or entire graph if no selection</x:v>
-      </x:c>
-      <x:c r="D16" s="19" t="str">
+      <x:c r="E21" s="105" t="str">
+        <x:v>No selection change</x:v>
+      </x:c>
+      <x:c r="F21" s="105" t="str">
+        <x:v>Graph / selection / local target</x:v>
+      </x:c>
+      <x:c r="G21" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="101" t="str">
+        <x:v>Long press</x:v>
+      </x:c>
+      <x:c r="B22" s="101" t="str">
+        <x:v>Node</x:v>
+      </x:c>
+      <x:c r="C22" s="101" t="str">
+        <x:v>Open node context menu</x:v>
+      </x:c>
+      <x:c r="D22" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E16" s="19" t="str">
-        <x:v>Preserve selection; set focus point to the current target centroid</x:v>
-      </x:c>
-      <x:c r="F16" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="G16" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H16" s="19" t="str"/>
-    </x:row>
-    <x:row r="17" ht="43" customHeight="1">
-      <x:c r="A17" s="18" t="str">
-        <x:v>Long press</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
-        <x:v>Node</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="str">
-        <x:v>Open node context menu</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="str">
+      <x:c r="E22" s="101" t="str">
+        <x:v>No automatic state change</x:v>
+      </x:c>
+      <x:c r="F22" s="101" t="str">
+        <x:v>No automatic camera change</x:v>
+      </x:c>
+      <x:c r="G22" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="105" t="str">
+        <x:v>Gesture cancel</x:v>
+      </x:c>
+      <x:c r="B23" s="105" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="C23" s="105" t="str">
+        <x:v>Stop without tap activation</x:v>
+      </x:c>
+      <x:c r="D23" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
-      <x:c r="E17" s="18" t="str">
-        <x:v>Preserve selection</x:v>
-      </x:c>
-      <x:c r="F17" s="18" t="str">
-        <x:v>Verify assumption</x:v>
-      </x:c>
-      <x:c r="G17" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H17" s="18" t="str"/>
-    </x:row>
-    <x:row r="18" ht="43" customHeight="1">
-      <x:c r="A18" s="19" t="str">
-        <x:v>Add second finger during long press</x:v>
-      </x:c>
-      <x:c r="B18" s="19" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C18" s="19" t="str">
-        <x:v>Cancel long press</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E18" s="19" t="str">
-        <x:v>Begin two-finger arbitration</x:v>
-      </x:c>
-      <x:c r="F18" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G18" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H18" s="19" t="str"/>
-    </x:row>
-    <x:row r="19" ht="43" customHeight="1">
-      <x:c r="A19" s="18" t="str">
-        <x:v>Move more than 6 px during long press</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C19" s="18" t="str">
-        <x:v>Cancel long press</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E19" s="18" t="str">
-        <x:v>Gesture becomes navigation</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G19" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H19" s="18" t="str"/>
-    </x:row>
-    <x:row r="20" ht="43" customHeight="1">
-      <x:c r="A20" s="19" t="str">
-        <x:v>Gesture cancellation</x:v>
-      </x:c>
-      <x:c r="B20" s="19" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C20" s="19" t="str">
-        <x:v>Stop without tap activation</x:v>
-      </x:c>
-      <x:c r="D20" s="19" t="str">
-        <x:v>Same</x:v>
-      </x:c>
-      <x:c r="E20" s="19" t="str">
+      <x:c r="E23" s="105" t="str">
+        <x:v>Clear transient input only</x:v>
+      </x:c>
+      <x:c r="F23" s="105" t="str">
         <x:v>No activation</x:v>
       </x:c>
-      <x:c r="F20" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="G20" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="H20" s="19" t="str"/>
+      <x:c r="G23" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G6:G20">
@@ -5748,130 +6993,209 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb41ee173fbfa42d4"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="43" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
-        <x:v>Mobile two-finger gesture contract</x:v>
-      </x:c>
+      <x:c r="A2" s="84" t="str">
+        <x:v>Mobile two-finger inputs</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Starting over a node or the background is irrelevant. Moving both fingers together is translation; changing the distance between them is pinch zoom.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Starting over a node or background is irrelevant; translation and pinch are measured independently.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Gesture</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Starting target</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>2D</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>3D no selection</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>3D selection exists</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Selection and camera-focus effect</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="I5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
-        <x:v>Move both fingers together</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
+      <x:c r="B5" s="99" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>2D behavior</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="str">
+        <x:v>3D behavior</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>Selection / Focus effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Translate both fingers</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Overview</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="str">
+      <x:c r="D6" s="101" t="str">
         <x:v>Rotate</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="str">
+      <x:c r="E6" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Translate both fingers</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
         <x:v>Pan</x:v>
       </x:c>
-      <x:c r="F6" s="19" t="str">
-        <x:v>Preserve selection; pan changes its offset from the stored focus point</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="H6" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="I6" s="19"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Change distance between fingers</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Anywhere</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Zoom</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Zoom</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Zoom</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>Preserve selection and stored focus point</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str">
-        <x:v>Confirmed correction</x:v>
-      </x:c>
-      <x:c r="H7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="I7" s="18"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="70"/>
-      <x:c r="B8" s="70"/>
-      <x:c r="C8" s="70"/>
-      <x:c r="D8" s="70"/>
-      <x:c r="E8" s="70"/>
-      <x:c r="F8" s="70"/>
-      <x:c r="G8" s="73"/>
-      <x:c r="H8" s="70"/>
-      <x:c r="I8" s="70"/>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str">
+        <x:v>Retain constellation</x:v>
+      </x:c>
+      <x:c r="F7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Translate both fingers</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Radial zoom</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>Gesture centroid controls distance from focused node</x:v>
+      </x:c>
+      <x:c r="F8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Change finger separation</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Overview or Explore</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Pinch zoom around centroid</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>State retained</x:v>
+      </x:c>
+      <x:c r="F9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Change finger separation</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Pinch zoom + radial translation</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Both controls apply simultaneously</x:v>
+      </x:c>
+      <x:c r="F10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Add second finger during long press</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Cancel long press; begin two-finger arbitration</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>No context menu activation</x:v>
+      </x:c>
+      <x:c r="F11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="H6:H7">
@@ -5921,124 +7245,194 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b2682192f434969"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="82" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
+      <x:c r="A2" s="84" t="str">
         <x:v>Stylus inputs</x:v>
       </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
+      <x:c r="F2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Stylus behavior follows the direct non-mouse input path where the device supplies pointer events.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Stylus follows direct pointer semantics when the platform supplies pen pointer events.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+      <x:c r="F3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+      <x:c r="F4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Input</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Behavior</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
-        <x:v>Stylus tap</x:v>
-      </x:c>
-      <x:c r="B6" s="19" t="str">
-        <x:v>Same node or background result as a primary click; no 320 ms touch delay</x:v>
-      </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="D6" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Stylus drag on a selected node</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Drag node; translate focus point by the selection-centroid delta without refitting</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
-        <x:v>Stylus long press on background</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Center + Fit selection, or graph if no selection; set focus point to the target centroid</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Stylus long press on node</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Open context menu</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Verify assumption</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="19" t="str">
-        <x:v>Stylus hover when supported</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="str">
-        <x:v>Node hover; note preview remains mouse-and-modifier-specific</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="str"/>
+      <x:c r="B5" s="99" t="str">
+        <x:v>Target / state</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>2D behavior</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="str">
+        <x:v>3D behavior</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>State effect</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
+        <x:v>Tap</x:v>
+      </x:c>
+      <x:c r="B6" s="101" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Use stationary pointer state transitions</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="str">
+        <x:v>Matches desktop primary click</x:v>
+      </x:c>
+      <x:c r="F6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Drag</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
+        <x:v>Overview or Explore selected node</x:v>
+      </x:c>
+      <x:c r="C7" s="105" t="str">
+        <x:v>Drag node</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Drag node</x:v>
+      </x:c>
+      <x:c r="E7" s="105" t="str">
+        <x:v>Direct pen manipulation remains available</x:v>
+      </x:c>
+      <x:c r="F7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
+        <x:v>Drag</x:v>
+      </x:c>
+      <x:c r="B8" s="101" t="str">
+        <x:v>Background / Overview</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="E8" s="101" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="F8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Drag</x:v>
+      </x:c>
+      <x:c r="B9" s="105" t="str">
+        <x:v>Background / Explore</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Pan</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E9" s="105" t="str">
+        <x:v>Retain selection</x:v>
+      </x:c>
+      <x:c r="F9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Drag</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C10" s="101" t="str">
+        <x:v>Elastic pan</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Rotate</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>Retain Focus</x:v>
+      </x:c>
+      <x:c r="F10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
+        <x:v>Long press</x:v>
+      </x:c>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Node / background</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Context menu / state Center + Fit</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Same</x:v>
+      </x:c>
+      <x:c r="E11" s="105" t="str">
+        <x:v>Stationary target split</x:v>
+      </x:c>
+      <x:c r="F11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D10">
@@ -6056,162 +7450,217 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f5c1c785de347fd"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF496A8A"/>
+    <x:tabColor rgb="FF24384D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="67" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="1" t="str">
-        <x:v>Center + Fit camera contract</x:v>
-      </x:c>
+      <x:c r="A2" s="84" t="str">
+        <x:v>Center, Fit, and Focus zoom limits</x:v>
+      </x:c>
+      <x:c r="B2" s="84"/>
+      <x:c r="C2" s="84"/>
+      <x:c r="D2" s="84"/>
+      <x:c r="E2" s="84"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>Center + Fit composes two actions. Center translates to the target centroid without changing zoom. Fit adjusts zoom to contain the same target. The target is the selection when one exists, otherwise the graph. An empty graph is a no-op.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="A3" s="85" t="str">
+        <x:v>Center never resets camera angle. Fit never changes the chosen target.</x:v>
+      </x:c>
+      <x:c r="B3" s="85"/>
+      <x:c r="C3" s="85"/>
+      <x:c r="D3" s="85"/>
+      <x:c r="E3" s="85"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="83"/>
+      <x:c r="B4" s="83"/>
+      <x:c r="C4" s="83"/>
+      <x:c r="D4" s="83"/>
+      <x:c r="E4" s="83"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="99" t="str">
         <x:v>Action</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>Condition or target</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="B5" s="99" t="str">
+        <x:v>Target</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
         <x:v>Operation</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="99" t="str">
         <x:v>Must remain unchanged</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Contract status</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>Review decision</x:v>
-      </x:c>
-      <x:c r="G5" s="17" t="str">
-        <x:v>Reviewer notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="43" customHeight="1">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="E5" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="101" t="str">
         <x:v>Center</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
+      <x:c r="B6" s="101" t="str">
+        <x:v>Graph</x:v>
+      </x:c>
+      <x:c r="C6" s="101" t="str">
+        <x:v>Translate camera target to graph centroid</x:v>
+      </x:c>
+      <x:c r="D6" s="101" t="str">
+        <x:v>Angle, up vector, zoom, distance</x:v>
+      </x:c>
+      <x:c r="E6" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="105" t="str">
+        <x:v>Center</x:v>
+      </x:c>
+      <x:c r="B7" s="105" t="str">
         <x:v>Selection</x:v>
       </x:c>
-      <x:c r="C6" s="19" t="str">
-        <x:v>Translate camera position and focus point to the selection centroid</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="str">
-        <x:v>Angle, orientation, up vector, zoom, and distance</x:v>
-      </x:c>
-      <x:c r="E6" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F6" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G6" s="19"/>
-    </x:row>
-    <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="C7" s="105" t="str">
+        <x:v>Translate camera target to selection centroid</x:v>
+      </x:c>
+      <x:c r="D7" s="105" t="str">
+        <x:v>Angle, up vector, zoom, distance</x:v>
+      </x:c>
+      <x:c r="E7" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="101" t="str">
         <x:v>Center</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Empty graph</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>No-op</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Entire camera state</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G7" s="18"/>
-    </x:row>
-    <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="19" t="str">
-        <x:v>Center</x:v>
-      </x:c>
-      <x:c r="B8" s="19" t="str">
-        <x:v>Entire graph</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="str">
-        <x:v>Translate camera position and focus point to the graph centroid</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="str">
-        <x:v>Angle, orientation, up vector, zoom, and distance</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F8" s="20" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G8" s="19"/>
-    </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="71" t="str">
+      <x:c r="B8" s="101" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C8" s="101" t="str">
+        <x:v>Translate camera target to focused node</x:v>
+      </x:c>
+      <x:c r="D8" s="101" t="str">
+        <x:v>Angle, up vector, zoom, distance</x:v>
+      </x:c>
+      <x:c r="E8" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="105" t="str">
         <x:v>Fit</x:v>
       </x:c>
-      <x:c r="B9" s="71" t="str">
+      <x:c r="B9" s="105" t="str">
+        <x:v>Graph</x:v>
+      </x:c>
+      <x:c r="C9" s="105" t="str">
+        <x:v>Adjust zoom / distance to fit graph</x:v>
+      </x:c>
+      <x:c r="D9" s="105" t="str">
+        <x:v>Target, angle, up vector</x:v>
+      </x:c>
+      <x:c r="E9" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="101" t="str">
+        <x:v>Fit</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
         <x:v>Selection</x:v>
       </x:c>
-      <x:c r="C9" s="71" t="str">
-        <x:v>Adjust camera zoom to fit selection</x:v>
-      </x:c>
-      <x:c r="D9" s="71" t="str">
-        <x:v>Target centroid, angle, orientation, and up vector</x:v>
-      </x:c>
-      <x:c r="E9" s="73" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F9" s="71" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G9" s="71"/>
-    </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="70" t="str">
+      <x:c r="C10" s="101" t="str">
+        <x:v>Adjust zoom / distance to fit selected nodes</x:v>
+      </x:c>
+      <x:c r="D10" s="101" t="str">
+        <x:v>Target, angle, up vector</x:v>
+      </x:c>
+      <x:c r="E10" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="105" t="str">
         <x:v>Fit</x:v>
       </x:c>
-      <x:c r="B10" s="70" t="str">
-        <x:v>Entire graph</x:v>
-      </x:c>
-      <x:c r="C10" s="70" t="str">
-        <x:v>Adjust camera zoom to fit graph</x:v>
-      </x:c>
-      <x:c r="D10" s="70" t="str">
-        <x:v>Target centroid, angle, orientation, and up vector</x:v>
-      </x:c>
-      <x:c r="E10" s="73" t="str">
-        <x:v>Confirmed requirement</x:v>
-      </x:c>
-      <x:c r="F10" s="70" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-      <x:c r="G10" s="70"/>
+      <x:c r="B11" s="105" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C11" s="105" t="str">
+        <x:v>Fit focused node plus immediate neighbors, centered on node</x:v>
+      </x:c>
+      <x:c r="D11" s="105" t="str">
+        <x:v>Angle, up vector</x:v>
+      </x:c>
+      <x:c r="E11" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>Center + Fit</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>State-owned target</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>Perform Center, then Fit as separate ordered actions</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>Angle and up vector</x:v>
+      </x:c>
+      <x:c r="E12" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="105" t="str">
+        <x:v>Zoom-out limit</x:v>
+      </x:c>
+      <x:c r="B13" s="105" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="C13" s="105" t="str">
+        <x:v>Longest distance from focused node to farthest selected node + padding; local entry fit remains valid baseline</x:v>
+      </x:c>
+      <x:c r="D13" s="105" t="str">
+        <x:v>Focus target</x:v>
+      </x:c>
+      <x:c r="E13" s="103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F6:F8">
@@ -6287,5 +7736,8 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8b60d49eaf4daf"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="Rcfd0f9b4156c4995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rdd49707a76cb4b93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="Rdcf6c81473214bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R11c0f3b7a157433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="Ra2c6f2646cee46c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="R54a5b1f2059040d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R5e7a25f455b2438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="R4324de4c009c4e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R3cf89ac732934a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Rf89cde0c37f74a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R49081ccca45e4558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R322368a5ede9427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="Rcaa7840dae554503"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R829c9ad958fc431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Policies" sheetId="15" r:id="Rf0ccd3ada4664672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="16" r:id="R0426697231f84912"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Focus Rendering" sheetId="17" r:id="R9623b98e3cb14706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R8cc5b61620864eea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rb85033a6d181416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R07cd7d55ef7a476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R3c19a54f1dbc4108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="R7ce3b2f2a906428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Re7ac96b293ed4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="Rd2463b5dcd0d4988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="Ra9e0cce182d5419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R818365b1f8fc4837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Reefb1635313048b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R70af8ee51a244a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R13f8e582173049af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R7553edd5b3774a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R8cf13a0cd7f84ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Policies" sheetId="15" r:id="Rc470dda50a7945f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="16" r:id="R675a458e26314751"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Focus Rendering" sheetId="17" r:id="R2f741878f89b4729"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3137,7 +3137,7 @@
         <x:v>All state-changing stationary activations</x:v>
       </x:c>
       <x:c r="C8" s="101" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="103" t="str">
         <x:v>Approved</x:v>
@@ -3360,7 +3360,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd118e2cbf286437c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea1b0e8c1b145f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3519,7 +3519,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4433e7ef8205426d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb502d435a5244c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4320,7 +4320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a37b8e369f548e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a39c9bc09b4f29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4419,7 +4419,7 @@
         <x:v>Whole graph</x:v>
       </x:c>
       <x:c r="F6" s="101" t="str">
-        <x:v>Whole graph</x:v>
+        <x:v>Whole graph; context normal</x:v>
       </x:c>
       <x:c r="G6" s="101" t="str">
         <x:v>Pan</x:v>
@@ -4445,7 +4445,7 @@
         <x:v>Selection</x:v>
       </x:c>
       <x:c r="F7" s="105" t="str">
-        <x:v>Graph with selection emphasis</x:v>
+        <x:v>Whole graph; selection highlighted, context dimmed</x:v>
       </x:c>
       <x:c r="G7" s="105" t="str">
         <x:v>Pan</x:v>
@@ -4471,7 +4471,7 @@
         <x:v>Focused node + immediate neighbors</x:v>
       </x:c>
       <x:c r="F8" s="101" t="str">
-        <x:v>Focused local view</x:v>
+        <x:v>Focused local view; local highlighted, other context hidden</x:v>
       </x:c>
       <x:c r="G8" s="101" t="str">
         <x:v>Elastic pan</x:v>
@@ -4483,7 +4483,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ff5286e68945e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5965d5a41445ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4788,10 +4788,33 @@
         <x:v>No implicit fit</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Focus</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Release Ctrl</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Selection grew from 0 or 1 node to 2+</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Explore</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Retain</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Preserve current framing</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d6d506f44244e33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3384864ddc43436b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4819,7 +4842,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="85" t="str">
-        <x:v>Focus keeps the constellation legible, grays the local neighborhood, and removes everything else.</x:v>
+        <x:v>Focus highlights its local neighborhood and selected constellation, and removes everything else.</x:v>
       </x:c>
       <x:c r="B3" s="85"/>
       <x:c r="C3" s="85"/>
@@ -4864,13 +4887,13 @@
         <x:v>Focused node, selected</x:v>
       </x:c>
       <x:c r="B7" s="105" t="str">
-        <x:v>Rendered and lit</x:v>
+        <x:v>Rendered and highlighted</x:v>
       </x:c>
       <x:c r="C7" s="105" t="str">
         <x:v>Normal local label policy</x:v>
       </x:c>
       <x:c r="D7" s="105" t="str">
-        <x:v>Focus-neighbor links remain</x:v>
+        <x:v>Focus-neighbor links highlighted</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -4878,13 +4901,13 @@
         <x:v>Focused node, unselected</x:v>
       </x:c>
       <x:c r="B8" s="101" t="str">
-        <x:v>Rendered gray; no focus-specific selection color</x:v>
+        <x:v>Rendered and highlighted</x:v>
       </x:c>
       <x:c r="C8" s="101" t="str">
         <x:v>Normal local label policy</x:v>
       </x:c>
       <x:c r="D8" s="101" t="str">
-        <x:v>Focus-neighbor links gray unless selected-selected</x:v>
+        <x:v>Focus-neighbor links highlighted</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -4892,13 +4915,13 @@
         <x:v>Immediate neighbor, unselected</x:v>
       </x:c>
       <x:c r="B9" s="105" t="str">
-        <x:v>Rendered gray</x:v>
+        <x:v>Rendered and highlighted</x:v>
       </x:c>
       <x:c r="C9" s="105" t="str">
         <x:v>Normal local label policy</x:v>
       </x:c>
       <x:c r="D9" s="105" t="str">
-        <x:v>Link to focused node rendered gray</x:v>
+        <x:v>Link to focused node highlighted</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -4932,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83262f55c73443cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948082b1a2fc4200"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5253,7 +5276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dddb693191e419f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc2c730c512d455b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5632,10 +5655,10 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E18" s="101" t="str">
-        <x:v>Focus remains valid while selection non-empty</x:v>
+        <x:v>Focus retained while held; a new multi-node constellation enters Explore on release</x:v>
       </x:c>
       <x:c r="F18" s="101" t="str">
-        <x:v>No camera change while held</x:v>
+        <x:v>No camera change while held or on release</x:v>
       </x:c>
       <x:c r="G18" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5883,7 +5906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7be154686bda4921"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6fb8f4964c7492b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6150,7 +6173,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reded927e8614411e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9120c1510cae48ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6312,16 +6335,16 @@
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="105" t="str">
-        <x:v>Release Ctrl after initial selection</x:v>
+        <x:v>Release Ctrl after zero/one-node selection</x:v>
       </x:c>
       <x:c r="B11" s="105" t="str">
-        <x:v>Center + Fit result</x:v>
+        <x:v>One node: Center + Fit Focus; multiple nodes: preserve framing</x:v>
       </x:c>
       <x:c r="C11" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D11" s="105" t="str">
-        <x:v>Use resulting state target</x:v>
+        <x:v>One node: Focus; multiple nodes: Explore</x:v>
       </x:c>
       <x:c r="E11" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6331,7 +6354,7 @@
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="101" t="str">
-        <x:v>Release Ctrl after existing-selection edits</x:v>
+        <x:v>Release Ctrl after established multi-selection edits</x:v>
       </x:c>
       <x:c r="B12" s="101" t="str">
         <x:v>No camera change</x:v>
@@ -6340,7 +6363,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D12" s="101" t="str">
-        <x:v>Retain changes and Focus</x:v>
+        <x:v>Retain changes and current Explore / Focus state</x:v>
       </x:c>
       <x:c r="E12" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6471,7 +6494,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05cc6e7d69be4db8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6c4d28e3494f41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6994,7 +7017,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb41ee173fbfa42d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6512245eec074c8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7246,7 +7269,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b2682192f434969"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b4c0392e2544ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7451,7 +7474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f5c1c785de347fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b24e672e984aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7737,7 +7760,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8b60d49eaf4daf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R334f2c0b86e240f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/graph-plus-ui-interaction-matrix.xlsx
+++ b/docs/graph-plus-ui-interaction-matrix.xlsx
@@ -2,23 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R8cc5b61620864eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="Rb85033a6d181416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R07cd7d55ef7a476e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R3c19a54f1dbc4108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="R7ce3b2f2a906428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Re7ac96b293ed4fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="Rd2463b5dcd0d4988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="Ra9e0cce182d5419d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R818365b1f8fc4837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="Reefb1635313048b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R70af8ee51a244a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="R13f8e582173049af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R7553edd5b3774a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R8cf13a0cd7f84ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Policies" sheetId="15" r:id="Rc470dda50a7945f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="16" r:id="R675a458e26314751"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Focus Rendering" sheetId="17" r:id="R2f741878f89b4729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Index" sheetId="1" r:id="R4de34eae769148ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Definitions" sheetId="2" r:id="R95d64a0f88ab4874"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Pointer" sheetId="3" r:id="R28e0af42b68740a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop Trackpad" sheetId="4" r:id="R58a78be2e03a4131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard" sheetId="5" r:id="R4ab25627cc3a4f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Touch" sheetId="6" r:id="Ra45ef81b19674e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile Two-Finger" sheetId="7" r:id="R503910370f1d472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stylus" sheetId="8" r:id="Rfd69a5401359485f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centering" sheetId="9" r:id="R96aa6f1ddefa4c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Context Menu" sheetId="10" r:id="R556779a393134775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings UI" sheetId="11" r:id="R623197351b5d468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Settings Controls" sheetId="12" r:id="Rd98b111ee0074696"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note Preview" sheetId="13" r:id="R5dbeb924a503420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Decisions" sheetId="14" r:id="R9fb8c82e3ad94898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Policies" sheetId="15" r:id="Rd3483e7b5b1c48f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Transitions" sheetId="16" r:id="R3516ce5ec02d4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Focus Rendering" sheetId="17" r:id="R2b8118181aba4f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explore Rendering" sheetId="18" r:id="R097d3123964b4cdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persistence" sheetId="19" r:id="R71ce9a51b74e427f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +31,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="14">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -108,8 +110,37 @@
       <x:color rgb="FF8A5B00"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF64748B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="44">
+  <x:fills count="50">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -326,8 +357,38 @@
         <x:fgColor rgb="FFFFF3D3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243B53"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243B53"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F3EA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -383,11 +444,25 @@
         <x:color rgb="FFCFD8E3"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD5DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD5DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD5DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD5DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="108">
+  <x:cellXfs count="138">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -694,6 +769,82 @@
     <x:xf numFmtId="0" fontId="13" fillId="43" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="46" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="47" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="47" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="47" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="48" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="48" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="49" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="49" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2662,7 +2813,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="ReviewIndexContract" displayName="ReviewIndexContract" ref="A5:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="ReviewIndexContract" displayName="ReviewIndexContract" ref="A5:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Worksheet"/>
     <x:tableColumn id="2" name="Scope"/>
@@ -2688,7 +2839,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="OpenDecisionsContract" displayName="OpenDecisionsContract" ref="A5:C8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="OpenDecisionsContract" displayName="OpenDecisionsContract" ref="A5:C10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Current decision"/>
@@ -3338,7 +3489,7 @@
         <x:v>Explicitly deferred follow-up design</x:v>
       </x:c>
       <x:c r="C21" s="105" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D21" s="103" t="str">
         <x:v>Approved</x:v>
@@ -3346,6 +3497,36 @@
       <x:c r="E21" s="105" t="str">
         <x:v>No contract inconsistency remains</x:v>
       </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="128" t="str">
+        <x:v>Explore Rendering</x:v>
+      </x:c>
+      <x:c r="B22" s="128" t="str">
+        <x:v>Constellation emphasis, context dimming, and hover inspection</x:v>
+      </x:c>
+      <x:c r="C22" s="128" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D22" s="137" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E22" s="128"/>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="133" t="str">
+        <x:v>Persistence</x:v>
+      </x:c>
+      <x:c r="B23" s="133" t="str">
+        <x:v>Saved-view restoration and initial framing</x:v>
+      </x:c>
+      <x:c r="C23" s="133" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D23" s="137" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="E23" s="133"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D6:D18">
@@ -3360,7 +3541,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea1b0e8c1b145f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98d7520c0c874cd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3519,7 +3700,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb502d435a5244c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca1e439087d24176"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4242,17 +4423,29 @@
       <x:c r="D8"/>
       <x:c r="E8"/>
     </x:row>
-    <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="128" t="str">
+        <x:v>Anima hover resistance</x:v>
+      </x:c>
+      <x:c r="B9" s="128" t="str">
+        <x:v>Require dwell and movement resistance before a dim Explore node becomes transiently lit; immediate hover remains the interim behavior.</x:v>
+      </x:c>
+      <x:c r="C9" s="135" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
       <x:c r="D9"/>
       <x:c r="E9"/>
     </x:row>
-    <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10"/>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="133" t="str">
+        <x:v>Shading and color language</x:v>
+      </x:c>
+      <x:c r="B10" s="133" t="str">
+        <x:v>Develop a shared Anima shading and color language; current Explore baseline is 24% opacity with 80% desaturation.</x:v>
+      </x:c>
+      <x:c r="C10" s="135" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
       <x:c r="D10"/>
       <x:c r="E10"/>
     </x:row>
@@ -4320,7 +4513,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a39c9bc09b4f29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c98c68a33e64c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4451,7 +4644,7 @@
         <x:v>Pan</x:v>
       </x:c>
       <x:c r="H7" s="105" t="str">
-        <x:v>Rotate</x:v>
+        <x:v>Pan</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -4483,7 +4676,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5965d5a41445ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f0245106f964a16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4569,16 +4762,16 @@
         <x:v>Any visible node</x:v>
       </x:c>
       <x:c r="D6" s="101" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Explore</x:v>
       </x:c>
       <x:c r="E6" s="101" t="str">
         <x:v>Select node</x:v>
       </x:c>
       <x:c r="F6" s="101" t="str">
-        <x:v>Focus clicked node</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="G6" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -4615,16 +4808,16 @@
         <x:v>Stationary</x:v>
       </x:c>
       <x:c r="D8" s="101" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Explore or Overview</x:v>
       </x:c>
       <x:c r="E8" s="101" t="str">
-        <x:v>No change</x:v>
+        <x:v>Remove clicked node</x:v>
       </x:c>
       <x:c r="F8" s="101" t="str">
-        <x:v>Focus clicked node</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="G8" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -4647,7 +4840,7 @@
         <x:v>Clear</x:v>
       </x:c>
       <x:c r="G9" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -4655,22 +4848,22 @@
         <x:v>Focus</x:v>
       </x:c>
       <x:c r="B10" s="101" t="str">
-        <x:v>Click different visible node</x:v>
+        <x:v>Click unselected node</x:v>
       </x:c>
       <x:c r="C10" s="101" t="str">
         <x:v>Stationary</x:v>
       </x:c>
       <x:c r="D10" s="101" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Explore</x:v>
       </x:c>
       <x:c r="E10" s="101" t="str">
-        <x:v>No change</x:v>
+        <x:v>Add node + shortest-path bridge</x:v>
       </x:c>
       <x:c r="F10" s="101" t="str">
-        <x:v>Hop to clicked node</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="G10" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -4678,22 +4871,22 @@
         <x:v>Focus</x:v>
       </x:c>
       <x:c r="B11" s="105" t="str">
-        <x:v>Single click focused node</x:v>
+        <x:v>Click selected node</x:v>
       </x:c>
       <x:c r="C11" s="105" t="str">
-        <x:v>After double-click arbitration</x:v>
+        <x:v>Stationary after double-click arbitration</x:v>
       </x:c>
       <x:c r="D11" s="105" t="str">
-        <x:v>Focus or Overview</x:v>
+        <x:v>Explore or Overview</x:v>
       </x:c>
       <x:c r="E11" s="105" t="str">
-        <x:v>Toggle focused node</x:v>
+        <x:v>Remove clicked node</x:v>
       </x:c>
       <x:c r="F11" s="105" t="str">
-        <x:v>Retain unless selection becomes empty</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="G11" s="105" t="str">
-        <x:v>Fit graph only if selection becomes empty</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -4716,7 +4909,7 @@
         <x:v>Clear</x:v>
       </x:c>
       <x:c r="G12" s="101" t="str">
-        <x:v>Center + Fit selection</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
@@ -4739,7 +4932,7 @@
         <x:v>Clear</x:v>
       </x:c>
       <x:c r="G13" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -4747,16 +4940,16 @@
         <x:v>Any</x:v>
       </x:c>
       <x:c r="B14" s="101" t="str">
-        <x:v>Double-click / tap focused node</x:v>
+        <x:v>Double-click / tap node</x:v>
       </x:c>
       <x:c r="C14" s="101" t="str">
-        <x:v>Focused before first activation</x:v>
+        <x:v>Same node twice without drag</x:v>
       </x:c>
       <x:c r="D14" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E14" s="101" t="str">
-        <x:v>No change</x:v>
+        <x:v>Leave node selected</x:v>
       </x:c>
       <x:c r="F14" s="101" t="str">
         <x:v>No change</x:v>
@@ -4790,31 +4983,31 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Any</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>Release Ctrl</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Selection grew from 0 or 1 node to 2+</x:v>
+        <x:v>Any selection</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>Explore</x:v>
+        <x:v>Same</x:v>
       </x:c>
       <x:c r="E16" t="str">
         <x:v>Retain</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>Clear</x:v>
+        <x:v>No change</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>Preserve current framing</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3384864ddc43436b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra939a9afc2274ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,8 +5148,263 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948082b1a2fc4200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5833709323ba46ae"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="31.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31.670000076293945" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="110" t="str">
+        <x:v>Explore / Constellation rendering</x:v>
+      </x:c>
+      <x:c r="B2" s="109"/>
+      <x:c r="C2" s="109"/>
+      <x:c r="D2" s="109"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="112" t="str">
+        <x:v>Selected structure remains durable; dim graph context stays inspectable without changing selection.</x:v>
+      </x:c>
+      <x:c r="B3" s="109"/>
+      <x:c r="C3" s="109"/>
+      <x:c r="D3" s="109"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="109"/>
+      <x:c r="B4" s="109"/>
+      <x:c r="C4" s="109"/>
+      <x:c r="D4" s="109"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="123" t="str">
+        <x:v>Element</x:v>
+      </x:c>
+      <x:c r="B5" s="123" t="str">
+        <x:v>Node presentation</x:v>
+      </x:c>
+      <x:c r="C5" s="123" t="str">
+        <x:v>Label presentation</x:v>
+      </x:c>
+      <x:c r="D5" s="123" t="str">
+        <x:v>Link presentation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="118" t="str">
+        <x:v>Selected constellation node</x:v>
+      </x:c>
+      <x:c r="B6" s="118" t="str">
+        <x:v>Full opacity; accent highlight</x:v>
+      </x:c>
+      <x:c r="C6" s="118" t="str">
+        <x:v>Selected emphasis</x:v>
+      </x:c>
+      <x:c r="D6" s="118" t="str">
+        <x:v>Selected-to-selected links lit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="118" t="str">
+        <x:v>Unselected context node</x:v>
+      </x:c>
+      <x:c r="B7" s="118" t="str">
+        <x:v>24% opacity; ordinary theme color with 80% desaturation</x:v>
+      </x:c>
+      <x:c r="C7" s="118" t="str">
+        <x:v>Normal adaptive policy; dim context</x:v>
+      </x:c>
+      <x:c r="D7" s="118" t="str">
+        <x:v>Incident links remain dim</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="118" t="str">
+        <x:v>Hovered context node</x:v>
+      </x:c>
+      <x:c r="B8" s="118" t="str">
+        <x:v>Transient full highlight; no selection change</x:v>
+      </x:c>
+      <x:c r="C8" s="118" t="str">
+        <x:v>Force hovered label visible</x:v>
+      </x:c>
+      <x:c r="D8" s="118" t="str">
+        <x:v>Neighbors, path, and incident links remain dim</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="118" t="str">
+        <x:v>Previewed or Option-revealed context</x:v>
+      </x:c>
+      <x:c r="B9" s="118" t="str">
+        <x:v>Remain dim outside the constellation</x:v>
+      </x:c>
+      <x:c r="C9" s="118" t="str">
+        <x:v>No automatic promotion</x:v>
+      </x:c>
+      <x:c r="D9" s="118" t="str">
+        <x:v>Remain dim</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="118" t="str">
+        <x:v>Hover resistance</x:v>
+      </x:c>
+      <x:c r="B10" s="118" t="str">
+        <x:v>Immediate interim behavior; dwell and movement resistance deferred to shared Anima animation kit</x:v>
+      </x:c>
+      <x:c r="C10" s="118" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+      <x:c r="D10" s="118" t="str">
+        <x:v>No state change</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A3:D3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.670000076293945" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="110" t="str">
+        <x:v>Saved view restoration</x:v>
+      </x:c>
+      <x:c r="B2" s="109"/>
+      <x:c r="C2" s="109"/>
+      <x:c r="D2" s="109"/>
+      <x:c r="E2" s="109"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="112" t="str">
+        <x:v>Loading a graph should return to its last compatible state without an automatic camera move.</x:v>
+      </x:c>
+      <x:c r="B3" s="109"/>
+      <x:c r="C3" s="109"/>
+      <x:c r="D3" s="109"/>
+      <x:c r="E3" s="109"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="109"/>
+      <x:c r="B4" s="109"/>
+      <x:c r="C4" s="109"/>
+      <x:c r="D4" s="109"/>
+      <x:c r="E4" s="109"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="123" t="str">
+        <x:v>Situation</x:v>
+      </x:c>
+      <x:c r="B5" s="123" t="str">
+        <x:v>Restored state</x:v>
+      </x:c>
+      <x:c r="C5" s="123" t="str">
+        <x:v>Camera behavior</x:v>
+      </x:c>
+      <x:c r="D5" s="123" t="str">
+        <x:v>Fallback</x:v>
+      </x:c>
+      <x:c r="E5" s="123" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="118" t="str">
+        <x:v>Compatible saved Graph+ view</x:v>
+      </x:c>
+      <x:c r="B6" s="118" t="str">
+        <x:v>Positions, pins, selection, Focus, filters, Form/module state</x:v>
+      </x:c>
+      <x:c r="C6" s="118" t="str">
+        <x:v>Restore saved framing; do not center or fit</x:v>
+      </x:c>
+      <x:c r="D6" s="118" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E6" s="118" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="118" t="str">
+        <x:v>Saved graph reconciles with vault</x:v>
+      </x:c>
+      <x:c r="B7" s="118" t="str">
+        <x:v>Reconcile by stable IDs</x:v>
+      </x:c>
+      <x:c r="C7" s="118" t="str">
+        <x:v>Preserve restored framing</x:v>
+      </x:c>
+      <x:c r="D7" s="118" t="str">
+        <x:v>Drop only incompatible IDs or state</x:v>
+      </x:c>
+      <x:c r="E7" s="118" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="118" t="str">
+        <x:v>No compatible saved view</x:v>
+      </x:c>
+      <x:c r="B8" s="118" t="str">
+        <x:v>Fresh Overview</x:v>
+      </x:c>
+      <x:c r="C8" s="118" t="str">
+        <x:v>Initial whole-graph fit</x:v>
+      </x:c>
+      <x:c r="D8" s="118" t="str">
+        <x:v>Generate finite positions</x:v>
+      </x:c>
+      <x:c r="E8" s="118" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="118" t="str">
+        <x:v>Explicit layout reset</x:v>
+      </x:c>
+      <x:c r="B9" s="118" t="str">
+        <x:v>Discard saved layout and interaction state</x:v>
+      </x:c>
+      <x:c r="C9" s="118" t="str">
+        <x:v>Explicit whole-graph fit is allowed</x:v>
+      </x:c>
+      <x:c r="D9" s="118" t="str">
+        <x:v>Create a fresh checkpoint</x:v>
+      </x:c>
+      <x:c r="E9" s="118" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -5129,7 +5577,7 @@
         <x:v>Changes framing without changing selection.</x:v>
       </x:c>
       <x:c r="D12" s="101" t="str">
-        <x:v>Normal in Overview and 2D Explore</x:v>
+        <x:v>Normal in Overview and Explore</x:v>
       </x:c>
       <x:c r="E12" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5163,7 +5611,7 @@
         <x:v>Changes angle without fitting or recentering.</x:v>
       </x:c>
       <x:c r="D14" s="101" t="str">
-        <x:v>Default 3D Explore and Focus navigation</x:v>
+        <x:v>Secondary drag in 3D Explore; primary navigation in 3D Focus</x:v>
       </x:c>
       <x:c r="E14" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5276,7 +5724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc2c730c512d455b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra30394f0d7f54ffa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5358,16 +5806,16 @@
         <x:v>Hover</x:v>
       </x:c>
       <x:c r="B6" s="101" t="str">
-        <x:v>Node / any state</x:v>
+        <x:v>Node / Overview or Explore</x:v>
       </x:c>
       <x:c r="C6" s="101" t="str">
-        <x:v>Highlight node</x:v>
+        <x:v>Highlight hovered node only</x:v>
       </x:c>
       <x:c r="D6" s="101" t="str">
-        <x:v>Highlight node</x:v>
+        <x:v>Highlight hovered node only</x:v>
       </x:c>
       <x:c r="E6" s="101" t="str">
-        <x:v>No state change</x:v>
+        <x:v>No selection change</x:v>
       </x:c>
       <x:c r="F6" s="101" t="str">
         <x:v>Transient only</x:v>
@@ -5442,7 +5890,7 @@
         <x:v>Enter Overview</x:v>
       </x:c>
       <x:c r="F9" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G9" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5466,7 +5914,7 @@
         <x:v>Enter Explore</x:v>
       </x:c>
       <x:c r="F10" s="101" t="str">
-        <x:v>Center + Fit selection</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G10" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5490,7 +5938,7 @@
         <x:v>Enter Overview</x:v>
       </x:c>
       <x:c r="F11" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G11" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5505,16 +5953,16 @@
         <x:v>Node / Overview</x:v>
       </x:c>
       <x:c r="C12" s="101" t="str">
-        <x:v>Select + Focus</x:v>
+        <x:v>Select; enter Explore</x:v>
       </x:c>
       <x:c r="D12" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E12" s="101" t="str">
-        <x:v>Enter Focus</x:v>
+        <x:v>Select node; clear Focus</x:v>
       </x:c>
       <x:c r="F12" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G12" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5553,16 +6001,16 @@
         <x:v>Selected node / Explore</x:v>
       </x:c>
       <x:c r="C14" s="101" t="str">
-        <x:v>Enter Focus</x:v>
+        <x:v>Remove node</x:v>
       </x:c>
       <x:c r="D14" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E14" s="101" t="str">
-        <x:v>Selection unchanged</x:v>
+        <x:v>Remain Explore, or Overview if empty</x:v>
       </x:c>
       <x:c r="F14" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G14" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5574,19 +6022,19 @@
         <x:v>Primary click</x:v>
       </x:c>
       <x:c r="B15" s="105" t="str">
-        <x:v>Different local node / Focus</x:v>
+        <x:v>Unselected node / Focus</x:v>
       </x:c>
       <x:c r="C15" s="105" t="str">
-        <x:v>Hop Focus</x:v>
+        <x:v>Add node + path bridge; exit Focus</x:v>
       </x:c>
       <x:c r="D15" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E15" s="105" t="str">
-        <x:v>Selection unchanged</x:v>
+        <x:v>Enter Explore</x:v>
       </x:c>
       <x:c r="F15" s="105" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G15" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5598,19 +6046,19 @@
         <x:v>Primary click</x:v>
       </x:c>
       <x:c r="B16" s="101" t="str">
-        <x:v>Focused node / Focus</x:v>
+        <x:v>Selected node / Focus</x:v>
       </x:c>
       <x:c r="C16" s="101" t="str">
-        <x:v>Toggle membership after double-click delay</x:v>
+        <x:v>Remove node; exit Focus</x:v>
       </x:c>
       <x:c r="D16" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E16" s="101" t="str">
-        <x:v>Focus independent of membership</x:v>
+        <x:v>Enter Explore, or Overview if empty</x:v>
       </x:c>
       <x:c r="F16" s="101" t="str">
-        <x:v>Graph fit only if selection empties</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G16" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5622,7 +6070,7 @@
         <x:v>Double click</x:v>
       </x:c>
       <x:c r="B17" s="105" t="str">
-        <x:v>Already-focused node</x:v>
+        <x:v>Node</x:v>
       </x:c>
       <x:c r="C17" s="105" t="str">
         <x:v>Primary node action</x:v>
@@ -5631,7 +6079,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E17" s="105" t="str">
-        <x:v>No state change</x:v>
+        <x:v>Leave node selected</x:v>
       </x:c>
       <x:c r="F17" s="105" t="str">
         <x:v>No camera change</x:v>
@@ -5649,16 +6097,16 @@
         <x:v>Node</x:v>
       </x:c>
       <x:c r="C18" s="101" t="str">
-        <x:v>Add / remove selection</x:v>
+        <x:v>Same as primary click</x:v>
       </x:c>
       <x:c r="D18" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E18" s="101" t="str">
-        <x:v>Focus retained while held; a new multi-node constellation enters Explore on release</x:v>
+        <x:v>Toggle constellation membership; clear Focus</x:v>
       </x:c>
       <x:c r="F18" s="101" t="str">
-        <x:v>No camera change while held or on release</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G18" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5700,13 +6148,13 @@
         <x:v>Pan</x:v>
       </x:c>
       <x:c r="D20" s="101" t="str">
-        <x:v>Rotate</x:v>
+        <x:v>Pan</x:v>
       </x:c>
       <x:c r="E20" s="101" t="str">
         <x:v>Retain selection</x:v>
       </x:c>
       <x:c r="F20" s="101" t="str">
-        <x:v>State-owned navigation</x:v>
+        <x:v>Translate camera</x:v>
       </x:c>
       <x:c r="G20" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -5906,7 +6354,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6fb8f4964c7492b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0764b7ff38d4250"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6173,7 +6621,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9120c1510cae48ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1421ca1168ba4d3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6319,13 +6767,13 @@
         <x:v>Hold Ctrl + node clicks</x:v>
       </x:c>
       <x:c r="B10" s="101" t="str">
-        <x:v>Edit selection</x:v>
+        <x:v>Same selection toggle as primary click</x:v>
       </x:c>
       <x:c r="C10" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D10" s="101" t="str">
-        <x:v>No camera change during edits</x:v>
+        <x:v>Additions include shortest path; no camera change</x:v>
       </x:c>
       <x:c r="E10" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6335,16 +6783,16 @@
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="105" t="str">
-        <x:v>Release Ctrl after zero/one-node selection</x:v>
+        <x:v>Release Ctrl</x:v>
       </x:c>
       <x:c r="B11" s="105" t="str">
-        <x:v>One node: Center + Fit Focus; multiple nodes: preserve framing</x:v>
+        <x:v>No change</x:v>
       </x:c>
       <x:c r="C11" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D11" s="105" t="str">
-        <x:v>One node: Focus; multiple nodes: Explore</x:v>
+        <x:v>Preserve selection, state, and framing</x:v>
       </x:c>
       <x:c r="E11" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6354,7 +6802,7 @@
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="101" t="str">
-        <x:v>Release Ctrl after established multi-selection edits</x:v>
+        <x:v>Release Ctrl after selection edits</x:v>
       </x:c>
       <x:c r="B12" s="101" t="str">
         <x:v>No camera change</x:v>
@@ -6363,7 +6811,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="D12" s="101" t="str">
-        <x:v>Retain changes and current Explore / Focus state</x:v>
+        <x:v>Preserve selection, state, and framing</x:v>
       </x:c>
       <x:c r="E12" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6376,7 +6824,7 @@
         <x:v>Hold Option</x:v>
       </x:c>
       <x:c r="B13" s="105" t="str">
-        <x:v>Reveal neighbors + connecting links</x:v>
+        <x:v>Preserve constellation-only highlighting</x:v>
       </x:c>
       <x:c r="C13" s="105" t="str">
         <x:v>Same</x:v>
@@ -6494,7 +6942,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6c4d28e3494f41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16d4aa6bb3ad4e1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6612,7 +7060,7 @@
         <x:v>Enter Overview</x:v>
       </x:c>
       <x:c r="F7" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G7" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6636,7 +7084,7 @@
         <x:v>Enter Explore</x:v>
       </x:c>
       <x:c r="F8" s="101" t="str">
-        <x:v>Center + Fit selection</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G8" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6660,7 +7108,7 @@
         <x:v>Enter Overview</x:v>
       </x:c>
       <x:c r="F9" s="105" t="str">
-        <x:v>Center + Fit graph</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G9" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6675,16 +7123,16 @@
         <x:v>Node / Overview</x:v>
       </x:c>
       <x:c r="C10" s="101" t="str">
-        <x:v>Select + Focus on release</x:v>
+        <x:v>Select on release; enter Explore</x:v>
       </x:c>
       <x:c r="D10" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E10" s="101" t="str">
-        <x:v>Enter Focus</x:v>
+        <x:v>Select node; clear Focus</x:v>
       </x:c>
       <x:c r="F10" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G10" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6696,19 +7144,19 @@
         <x:v>Tap</x:v>
       </x:c>
       <x:c r="B11" s="105" t="str">
-        <x:v>Selected node / Explore</x:v>
+        <x:v>Unselected node / Explore</x:v>
       </x:c>
       <x:c r="C11" s="105" t="str">
-        <x:v>Enter Focus</x:v>
+        <x:v>Add node + path bridge</x:v>
       </x:c>
       <x:c r="D11" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E11" s="105" t="str">
-        <x:v>Selection unchanged</x:v>
+        <x:v>Remain Explore</x:v>
       </x:c>
       <x:c r="F11" s="105" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G11" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6720,19 +7168,19 @@
         <x:v>Tap</x:v>
       </x:c>
       <x:c r="B12" s="101" t="str">
-        <x:v>Different local node / Focus</x:v>
+        <x:v>Selected node / Explore</x:v>
       </x:c>
       <x:c r="C12" s="101" t="str">
-        <x:v>Hop Focus</x:v>
+        <x:v>Remove node</x:v>
       </x:c>
       <x:c r="D12" s="101" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E12" s="101" t="str">
-        <x:v>Selection unchanged</x:v>
+        <x:v>Remain Explore, or Overview if empty</x:v>
       </x:c>
       <x:c r="F12" s="101" t="str">
-        <x:v>Center node; fit immediate neighbors</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G12" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6744,19 +7192,19 @@
         <x:v>Tap</x:v>
       </x:c>
       <x:c r="B13" s="105" t="str">
-        <x:v>Focused node / Focus</x:v>
+        <x:v>Any node / Focus</x:v>
       </x:c>
       <x:c r="C13" s="105" t="str">
-        <x:v>Toggle membership after double-tap delay</x:v>
+        <x:v>Toggle membership; exit Focus</x:v>
       </x:c>
       <x:c r="D13" s="105" t="str">
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E13" s="105" t="str">
-        <x:v>Focus independent of membership</x:v>
+        <x:v>Enter Explore, or Overview if empty</x:v>
       </x:c>
       <x:c r="F13" s="105" t="str">
-        <x:v>Graph fit only if selection empties</x:v>
+        <x:v>No camera change</x:v>
       </x:c>
       <x:c r="G13" s="103" t="str">
         <x:v>Implemented</x:v>
@@ -6774,7 +7222,7 @@
         <x:v>Pan</x:v>
       </x:c>
       <x:c r="D14" s="101" t="str">
-        <x:v>Rotate</x:v>
+        <x:v>Pan</x:v>
       </x:c>
       <x:c r="E14" s="101" t="str">
         <x:v>No selection or node drag</x:v>
@@ -6798,7 +7246,7 @@
         <x:v>Pan</x:v>
       </x:c>
       <x:c r="D15" s="105" t="str">
-        <x:v>Rotate</x:v>
+        <x:v>Pan</x:v>
       </x:c>
       <x:c r="E15" s="105" t="str">
         <x:v>Selection retained; no node drag</x:v>
@@ -6864,7 +7312,7 @@
         <x:v>Double tap</x:v>
       </x:c>
       <x:c r="B18" s="101" t="str">
-        <x:v>Already-focused node</x:v>
+        <x:v>Node</x:v>
       </x:c>
       <x:c r="C18" s="101" t="str">
         <x:v>Primary node action</x:v>
@@ -6873,7 +7321,7 @@
         <x:v>Same</x:v>
       </x:c>
       <x:c r="E18" s="101" t="str">
-        <x:v>No state change</x:v>
+        <x:v>Leave node selected</x:v>
       </x:c>
       <x:c r="F18" s="101" t="str">
         <x:v>No camera change</x:v>
@@ -7017,7 +7465,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6512245eec074c8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae5572ac29e4e03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7717,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b4c0392e2544ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe34b50de114424"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7474,7 +7922,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b24e672e984aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd222b9ad170643c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7760,7 +8208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R334f2c0b86e240f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8629f7996db74e7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>